--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118675822</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880445</v>
+        <v>119880471</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>91828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665752</v>
+        <v>665988</v>
       </c>
       <c r="R5" t="n">
-        <v>7185584</v>
+        <v>7185667</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880471</v>
+        <v>119880451</v>
       </c>
       <c r="B6" t="n">
-        <v>91828</v>
+        <v>78171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665988</v>
+        <v>665824</v>
       </c>
       <c r="R6" t="n">
-        <v>7185667</v>
+        <v>7185574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880431</v>
+        <v>119880468</v>
       </c>
       <c r="B7" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665509</v>
+        <v>665975</v>
       </c>
       <c r="R7" t="n">
-        <v>7185520</v>
+        <v>7185666</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880451</v>
+        <v>119880445</v>
       </c>
       <c r="B8" t="n">
         <v>78171</v>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665824</v>
+        <v>665752</v>
       </c>
       <c r="R8" t="n">
-        <v>7185574</v>
+        <v>7185584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880473</v>
+        <v>119880431</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666000</v>
+        <v>665509</v>
       </c>
       <c r="R9" t="n">
-        <v>7185668</v>
+        <v>7185520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880457</v>
+        <v>119880473</v>
       </c>
       <c r="B10" t="n">
         <v>91852</v>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665871</v>
+        <v>666000</v>
       </c>
       <c r="R10" t="n">
-        <v>7185570</v>
+        <v>7185668</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880468</v>
+        <v>119880457</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665975</v>
+        <v>665871</v>
       </c>
       <c r="R11" t="n">
-        <v>7185666</v>
+        <v>7185570</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880442</v>
+        <v>119880438</v>
       </c>
       <c r="B22" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665744</v>
+        <v>665723</v>
       </c>
       <c r="R22" t="n">
-        <v>7185572</v>
+        <v>7185514</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880438</v>
+        <v>119880442</v>
       </c>
       <c r="B23" t="n">
-        <v>91844</v>
+        <v>91834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,25 +2838,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665723</v>
+        <v>665744</v>
       </c>
       <c r="R23" t="n">
-        <v>7185514</v>
+        <v>7185572</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -3744,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880455</v>
+        <v>119880419</v>
       </c>
       <c r="B32" t="n">
-        <v>89275</v>
+        <v>78171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,25 +3756,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665872</v>
+        <v>665600</v>
       </c>
       <c r="R32" t="n">
-        <v>7185555</v>
+        <v>7185629</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880425</v>
+        <v>119880412</v>
       </c>
       <c r="B33" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665574</v>
+        <v>665642</v>
       </c>
       <c r="R33" t="n">
-        <v>7185592</v>
+        <v>7185682</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,7 +3948,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880419</v>
+        <v>119880414</v>
       </c>
       <c r="B34" t="n">
         <v>78171</v>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665600</v>
+        <v>665625</v>
       </c>
       <c r="R34" t="n">
-        <v>7185629</v>
+        <v>7185661</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880412</v>
+        <v>119880461</v>
       </c>
       <c r="B35" t="n">
-        <v>78171</v>
+        <v>91844</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4062,25 +4062,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665642</v>
+        <v>665905</v>
       </c>
       <c r="R35" t="n">
-        <v>7185682</v>
+        <v>7185598</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880414</v>
+        <v>119880455</v>
       </c>
       <c r="B36" t="n">
-        <v>78171</v>
+        <v>89275</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4164,25 +4164,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665625</v>
+        <v>665872</v>
       </c>
       <c r="R36" t="n">
-        <v>7185661</v>
+        <v>7185555</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880461</v>
+        <v>119880425</v>
       </c>
       <c r="B37" t="n">
-        <v>91844</v>
+        <v>89633</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4266,25 +4266,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665905</v>
+        <v>665574</v>
       </c>
       <c r="R37" t="n">
-        <v>7185598</v>
+        <v>7185592</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880429</v>
+        <v>119880439</v>
       </c>
       <c r="B39" t="n">
-        <v>91883</v>
+        <v>89633</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4474,21 +4474,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5448</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665527</v>
+        <v>665731</v>
       </c>
       <c r="R39" t="n">
-        <v>7185533</v>
+        <v>7185521</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,10 +4560,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880439</v>
+        <v>119880429</v>
       </c>
       <c r="B40" t="n">
-        <v>89633</v>
+        <v>91883</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4576,21 +4576,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>5448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665731</v>
+        <v>665527</v>
       </c>
       <c r="R40" t="n">
-        <v>7185521</v>
+        <v>7185533</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880424</v>
+        <v>119880417</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>77458</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5203,21 +5203,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>6487</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665577</v>
+        <v>665632</v>
       </c>
       <c r="R46" t="n">
-        <v>7185596</v>
+        <v>7185649</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880454</v>
+        <v>119880424</v>
       </c>
       <c r="B47" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665867</v>
+        <v>665577</v>
       </c>
       <c r="R47" t="n">
-        <v>7185544</v>
+        <v>7185596</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880417</v>
+        <v>119880454</v>
       </c>
       <c r="B48" t="n">
-        <v>77458</v>
+        <v>91832</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6487</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665632</v>
+        <v>665867</v>
       </c>
       <c r="R48" t="n">
-        <v>7185649</v>
+        <v>7185544</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880463</v>
+        <v>119880410</v>
       </c>
       <c r="B3" t="n">
-        <v>91826</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665918</v>
+        <v>665646</v>
       </c>
       <c r="R3" t="n">
-        <v>7185620</v>
+        <v>7185686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880452</v>
+        <v>119880471</v>
       </c>
       <c r="B4" t="n">
-        <v>91826</v>
+        <v>91828</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665842</v>
+        <v>665988</v>
       </c>
       <c r="R4" t="n">
-        <v>7185565</v>
+        <v>7185667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880471</v>
+        <v>119880465</v>
       </c>
       <c r="B5" t="n">
         <v>91828</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665988</v>
+        <v>665944</v>
       </c>
       <c r="R5" t="n">
-        <v>7185667</v>
+        <v>7185632</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880468</v>
+        <v>119880444</v>
       </c>
       <c r="B7" t="n">
-        <v>79144</v>
+        <v>89633</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665975</v>
+        <v>665746</v>
       </c>
       <c r="R7" t="n">
-        <v>7185666</v>
+        <v>7185579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880445</v>
+        <v>119880398</v>
       </c>
       <c r="B8" t="n">
-        <v>78171</v>
+        <v>89275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665752</v>
+        <v>665837</v>
       </c>
       <c r="R8" t="n">
-        <v>7185584</v>
+        <v>7185742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880431</v>
+        <v>119880470</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665509</v>
+        <v>665982</v>
       </c>
       <c r="R9" t="n">
-        <v>7185520</v>
+        <v>7185672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880473</v>
+        <v>119880461</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666000</v>
+        <v>665905</v>
       </c>
       <c r="R10" t="n">
-        <v>7185668</v>
+        <v>7185598</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880457</v>
+        <v>119880452</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665871</v>
+        <v>665842</v>
       </c>
       <c r="R11" t="n">
-        <v>7185570</v>
+        <v>7185565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880462</v>
+        <v>119880409</v>
       </c>
       <c r="B12" t="n">
-        <v>89252</v>
+        <v>89230</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>1596</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665918</v>
+        <v>665652</v>
       </c>
       <c r="R12" t="n">
-        <v>7185620</v>
+        <v>7185701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880410</v>
+        <v>119880460</v>
       </c>
       <c r="B13" t="n">
         <v>91832</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665646</v>
+        <v>665910</v>
       </c>
       <c r="R13" t="n">
-        <v>7185686</v>
+        <v>7185584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880448</v>
+        <v>119880454</v>
       </c>
       <c r="B14" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665801</v>
+        <v>665867</v>
       </c>
       <c r="R14" t="n">
-        <v>7185555</v>
+        <v>7185544</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880444</v>
+        <v>119880473</v>
       </c>
       <c r="B15" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665746</v>
+        <v>666000</v>
       </c>
       <c r="R15" t="n">
-        <v>7185579</v>
+        <v>7185668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,7 +2112,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880449</v>
+        <v>119880459</v>
       </c>
       <c r="B16" t="n">
         <v>78171</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665811</v>
+        <v>665913</v>
       </c>
       <c r="R16" t="n">
-        <v>7185566</v>
+        <v>7185574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880430</v>
+        <v>119880439</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665527</v>
+        <v>665731</v>
       </c>
       <c r="R17" t="n">
-        <v>7185533</v>
+        <v>7185521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880467</v>
+        <v>119880425</v>
       </c>
       <c r="B18" t="n">
-        <v>89252</v>
+        <v>89633</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665967</v>
+        <v>665574</v>
       </c>
       <c r="R18" t="n">
-        <v>7185660</v>
+        <v>7185592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880409</v>
+        <v>119880438</v>
       </c>
       <c r="B19" t="n">
-        <v>89230</v>
+        <v>91844</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1596</v>
+        <v>4365</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665652</v>
+        <v>665723</v>
       </c>
       <c r="R19" t="n">
-        <v>7185701</v>
+        <v>7185514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880470</v>
+        <v>119880419</v>
       </c>
       <c r="B20" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665982</v>
+        <v>665600</v>
       </c>
       <c r="R20" t="n">
-        <v>7185672</v>
+        <v>7185629</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880447</v>
+        <v>119880433</v>
       </c>
       <c r="B21" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665779</v>
+        <v>665516</v>
       </c>
       <c r="R21" t="n">
-        <v>7185591</v>
+        <v>7185504</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880438</v>
+        <v>119880467</v>
       </c>
       <c r="B22" t="n">
-        <v>91844</v>
+        <v>89252</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665723</v>
+        <v>665967</v>
       </c>
       <c r="R22" t="n">
-        <v>7185514</v>
+        <v>7185660</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880442</v>
+        <v>119880468</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>79144</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665744</v>
+        <v>665975</v>
       </c>
       <c r="R23" t="n">
-        <v>7185572</v>
+        <v>7185666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880440</v>
+        <v>119880457</v>
       </c>
       <c r="B24" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665733</v>
+        <v>665871</v>
       </c>
       <c r="R24" t="n">
-        <v>7185520</v>
+        <v>7185570</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880466</v>
+        <v>119880443</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665966</v>
+        <v>665746</v>
       </c>
       <c r="R25" t="n">
-        <v>7185634</v>
+        <v>7185579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880398</v>
+        <v>119880412</v>
       </c>
       <c r="B26" t="n">
-        <v>89275</v>
+        <v>78171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3144,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665837</v>
+        <v>665642</v>
       </c>
       <c r="R26" t="n">
-        <v>7185742</v>
+        <v>7185682</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880418</v>
+        <v>119880431</v>
       </c>
       <c r="B27" t="n">
-        <v>91852</v>
+        <v>78171</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3246,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665618</v>
+        <v>665509</v>
       </c>
       <c r="R27" t="n">
-        <v>7185647</v>
+        <v>7185520</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880464</v>
+        <v>119880453</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91826</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665922</v>
+        <v>665867</v>
       </c>
       <c r="R28" t="n">
-        <v>7185624</v>
+        <v>7185548</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880411</v>
+        <v>119880429</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,25 +3450,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665645</v>
+        <v>665527</v>
       </c>
       <c r="R29" t="n">
-        <v>7185685</v>
+        <v>7185533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880465</v>
+        <v>119880418</v>
       </c>
       <c r="B30" t="n">
-        <v>91828</v>
+        <v>91852</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,25 +3552,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665944</v>
+        <v>665618</v>
       </c>
       <c r="R30" t="n">
-        <v>7185632</v>
+        <v>7185647</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880427</v>
+        <v>119880442</v>
       </c>
       <c r="B31" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3658,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665573</v>
+        <v>665744</v>
       </c>
       <c r="R31" t="n">
-        <v>7185584</v>
+        <v>7185572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880419</v>
+        <v>119880423</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665600</v>
+        <v>665584</v>
       </c>
       <c r="R32" t="n">
-        <v>7185629</v>
+        <v>7185605</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880412</v>
+        <v>119880462</v>
       </c>
       <c r="B33" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,25 +3858,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665642</v>
+        <v>665918</v>
       </c>
       <c r="R33" t="n">
-        <v>7185682</v>
+        <v>7185620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880414</v>
+        <v>119880441</v>
       </c>
       <c r="B34" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665625</v>
+        <v>665740</v>
       </c>
       <c r="R34" t="n">
-        <v>7185661</v>
+        <v>7185522</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880461</v>
+        <v>119880430</v>
       </c>
       <c r="B35" t="n">
-        <v>91844</v>
+        <v>91832</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4062,25 +4062,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665905</v>
+        <v>665527</v>
       </c>
       <c r="R35" t="n">
-        <v>7185598</v>
+        <v>7185533</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880455</v>
+        <v>119880424</v>
       </c>
       <c r="B36" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4164,25 +4164,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665872</v>
+        <v>665577</v>
       </c>
       <c r="R36" t="n">
-        <v>7185555</v>
+        <v>7185596</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880425</v>
+        <v>119880447</v>
       </c>
       <c r="B37" t="n">
-        <v>89633</v>
+        <v>91856</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665574</v>
+        <v>665779</v>
       </c>
       <c r="R37" t="n">
-        <v>7185592</v>
+        <v>7185591</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880423</v>
+        <v>119880472</v>
       </c>
       <c r="B38" t="n">
-        <v>78263</v>
+        <v>91826</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>3100</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665584</v>
+        <v>665998</v>
       </c>
       <c r="R38" t="n">
-        <v>7185605</v>
+        <v>7185666</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880439</v>
+        <v>119880437</v>
       </c>
       <c r="B39" t="n">
-        <v>89633</v>
+        <v>79643</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4470,25 +4470,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665731</v>
+        <v>665631</v>
       </c>
       <c r="R39" t="n">
-        <v>7185521</v>
+        <v>7185482</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,6 +4544,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4560,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880429</v>
+        <v>119880446</v>
       </c>
       <c r="B40" t="n">
-        <v>91883</v>
+        <v>78171</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4576,21 +4591,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4600,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665527</v>
+        <v>665779</v>
       </c>
       <c r="R40" t="n">
-        <v>7185533</v>
+        <v>7185598</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880433</v>
+        <v>119880427</v>
       </c>
       <c r="B41" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4678,21 +4693,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4702,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665516</v>
+        <v>665573</v>
       </c>
       <c r="R41" t="n">
-        <v>7185504</v>
+        <v>7185584</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880413</v>
+        <v>119880448</v>
       </c>
       <c r="B42" t="n">
-        <v>89275</v>
+        <v>91834</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4776,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665629</v>
+        <v>665801</v>
       </c>
       <c r="R42" t="n">
-        <v>7185671</v>
+        <v>7185555</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880443</v>
+        <v>119880463</v>
       </c>
       <c r="B43" t="n">
-        <v>91852</v>
+        <v>91826</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4878,25 +4893,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4906,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665746</v>
+        <v>665918</v>
       </c>
       <c r="R43" t="n">
-        <v>7185579</v>
+        <v>7185620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880458</v>
+        <v>119880428</v>
       </c>
       <c r="B44" t="n">
-        <v>89252</v>
+        <v>91884</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4980,25 +4995,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5008,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665911</v>
+        <v>665530</v>
       </c>
       <c r="R44" t="n">
-        <v>7185565</v>
+        <v>7185543</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5070,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880437</v>
+        <v>119880456</v>
       </c>
       <c r="B45" t="n">
-        <v>79643</v>
+        <v>78171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5082,25 +5097,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665631</v>
+        <v>665872</v>
       </c>
       <c r="R45" t="n">
-        <v>7185482</v>
+        <v>7185563</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5156,21 +5171,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5187,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880417</v>
+        <v>119880466</v>
       </c>
       <c r="B46" t="n">
-        <v>77458</v>
+        <v>91832</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5203,21 +5203,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6487</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665632</v>
+        <v>665966</v>
       </c>
       <c r="R46" t="n">
-        <v>7185649</v>
+        <v>7185634</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880424</v>
+        <v>119880440</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665577</v>
+        <v>665733</v>
       </c>
       <c r="R47" t="n">
-        <v>7185596</v>
+        <v>7185520</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880454</v>
+        <v>119880455</v>
       </c>
       <c r="B48" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5403,25 +5403,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665867</v>
+        <v>665872</v>
       </c>
       <c r="R48" t="n">
-        <v>7185544</v>
+        <v>7185555</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880460</v>
+        <v>119880413</v>
       </c>
       <c r="B49" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,25 +5505,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665910</v>
+        <v>665629</v>
       </c>
       <c r="R49" t="n">
-        <v>7185584</v>
+        <v>7185671</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880450</v>
+        <v>119880411</v>
       </c>
       <c r="B50" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,25 +5607,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665811</v>
+        <v>665645</v>
       </c>
       <c r="R50" t="n">
-        <v>7185566</v>
+        <v>7185685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880453</v>
+        <v>119880445</v>
       </c>
       <c r="B51" t="n">
-        <v>91826</v>
+        <v>78171</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665867</v>
+        <v>665752</v>
       </c>
       <c r="R51" t="n">
-        <v>7185548</v>
+        <v>7185584</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880446</v>
+        <v>119880414</v>
       </c>
       <c r="B52" t="n">
         <v>78171</v>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665779</v>
+        <v>665625</v>
       </c>
       <c r="R52" t="n">
-        <v>7185598</v>
+        <v>7185661</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880456</v>
+        <v>119880450</v>
       </c>
       <c r="B53" t="n">
-        <v>78171</v>
+        <v>89633</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5917,21 +5917,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665872</v>
+        <v>665811</v>
       </c>
       <c r="R53" t="n">
-        <v>7185563</v>
+        <v>7185566</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880459</v>
+        <v>119880417</v>
       </c>
       <c r="B54" t="n">
-        <v>78171</v>
+        <v>77458</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6019,21 +6019,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665913</v>
+        <v>665632</v>
       </c>
       <c r="R54" t="n">
-        <v>7185574</v>
+        <v>7185649</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880472</v>
+        <v>119880464</v>
       </c>
       <c r="B55" t="n">
-        <v>91826</v>
+        <v>91852</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6117,25 +6117,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665998</v>
+        <v>665922</v>
       </c>
       <c r="R55" t="n">
-        <v>7185666</v>
+        <v>7185624</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880428</v>
+        <v>119880449</v>
       </c>
       <c r="B56" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665530</v>
+        <v>665811</v>
       </c>
       <c r="R56" t="n">
-        <v>7185543</v>
+        <v>7185566</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880441</v>
+        <v>119880458</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6321,25 +6321,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665740</v>
+        <v>665911</v>
       </c>
       <c r="R57" t="n">
-        <v>7185522</v>
+        <v>7185565</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880410</v>
+        <v>119880471</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665646</v>
+        <v>665988</v>
       </c>
       <c r="R3" t="n">
-        <v>7185686</v>
+        <v>7185667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880471</v>
+        <v>119880465</v>
       </c>
       <c r="B4" t="n">
         <v>91828</v>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665988</v>
+        <v>665944</v>
       </c>
       <c r="R4" t="n">
-        <v>7185667</v>
+        <v>7185632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880465</v>
+        <v>119880410</v>
       </c>
       <c r="B5" t="n">
-        <v>91828</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665944</v>
+        <v>665646</v>
       </c>
       <c r="R5" t="n">
-        <v>7185632</v>
+        <v>7185686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880461</v>
+        <v>119880452</v>
       </c>
       <c r="B10" t="n">
-        <v>91844</v>
+        <v>91826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665905</v>
+        <v>665842</v>
       </c>
       <c r="R10" t="n">
-        <v>7185598</v>
+        <v>7185565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880452</v>
+        <v>119880461</v>
       </c>
       <c r="B11" t="n">
-        <v>91826</v>
+        <v>91844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665842</v>
+        <v>665905</v>
       </c>
       <c r="R11" t="n">
-        <v>7185565</v>
+        <v>7185598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880409</v>
+        <v>119880460</v>
       </c>
       <c r="B12" t="n">
-        <v>89230</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1596</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665652</v>
+        <v>665910</v>
       </c>
       <c r="R12" t="n">
-        <v>7185701</v>
+        <v>7185584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880460</v>
+        <v>119880454</v>
       </c>
       <c r="B13" t="n">
         <v>91832</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665910</v>
+        <v>665867</v>
       </c>
       <c r="R13" t="n">
-        <v>7185584</v>
+        <v>7185544</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880454</v>
+        <v>119880409</v>
       </c>
       <c r="B14" t="n">
-        <v>91832</v>
+        <v>89230</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>1596</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665867</v>
+        <v>665652</v>
       </c>
       <c r="R14" t="n">
-        <v>7185544</v>
+        <v>7185701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880448</v>
+        <v>119880463</v>
       </c>
       <c r="B42" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665801</v>
+        <v>665918</v>
       </c>
       <c r="R42" t="n">
-        <v>7185555</v>
+        <v>7185620</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880463</v>
+        <v>119880448</v>
       </c>
       <c r="B43" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665918</v>
+        <v>665801</v>
       </c>
       <c r="R43" t="n">
-        <v>7185620</v>
+        <v>7185555</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880466</v>
+        <v>119880455</v>
       </c>
       <c r="B46" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,25 +5199,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665966</v>
+        <v>665872</v>
       </c>
       <c r="R46" t="n">
-        <v>7185634</v>
+        <v>7185555</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880440</v>
+        <v>119880466</v>
       </c>
       <c r="B47" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665733</v>
+        <v>665966</v>
       </c>
       <c r="R47" t="n">
-        <v>7185520</v>
+        <v>7185634</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880455</v>
+        <v>119880440</v>
       </c>
       <c r="B48" t="n">
-        <v>89275</v>
+        <v>78171</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5403,25 +5403,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665872</v>
+        <v>665733</v>
       </c>
       <c r="R48" t="n">
-        <v>7185555</v>
+        <v>7185520</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880413</v>
+        <v>119880411</v>
       </c>
       <c r="B49" t="n">
-        <v>89275</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,25 +5505,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665629</v>
+        <v>665645</v>
       </c>
       <c r="R49" t="n">
-        <v>7185671</v>
+        <v>7185685</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880411</v>
+        <v>119880413</v>
       </c>
       <c r="B50" t="n">
-        <v>91840</v>
+        <v>89275</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,25 +5607,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665645</v>
+        <v>665629</v>
       </c>
       <c r="R50" t="n">
-        <v>7185685</v>
+        <v>7185671</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880471</v>
+        <v>119880458</v>
       </c>
       <c r="B3" t="n">
-        <v>91828</v>
+        <v>89252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>149</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665988</v>
+        <v>665911</v>
       </c>
       <c r="R3" t="n">
-        <v>7185667</v>
+        <v>7185565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880465</v>
+        <v>119880449</v>
       </c>
       <c r="B4" t="n">
-        <v>91828</v>
+        <v>78171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665944</v>
+        <v>665811</v>
       </c>
       <c r="R4" t="n">
-        <v>7185632</v>
+        <v>7185566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880410</v>
+        <v>119880450</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665646</v>
+        <v>665811</v>
       </c>
       <c r="R5" t="n">
-        <v>7185686</v>
+        <v>7185566</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880451</v>
+        <v>119880457</v>
       </c>
       <c r="B6" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665824</v>
+        <v>665871</v>
       </c>
       <c r="R6" t="n">
-        <v>7185574</v>
+        <v>7185570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880444</v>
+        <v>119880464</v>
       </c>
       <c r="B7" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665746</v>
+        <v>665922</v>
       </c>
       <c r="R7" t="n">
-        <v>7185579</v>
+        <v>7185624</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880398</v>
+        <v>119880462</v>
       </c>
       <c r="B8" t="n">
-        <v>89275</v>
+        <v>89252</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665837</v>
+        <v>665918</v>
       </c>
       <c r="R8" t="n">
-        <v>7185742</v>
+        <v>7185620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880470</v>
+        <v>119880431</v>
       </c>
       <c r="B9" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665982</v>
+        <v>665509</v>
       </c>
       <c r="R9" t="n">
-        <v>7185672</v>
+        <v>7185520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880452</v>
+        <v>119880437</v>
       </c>
       <c r="B10" t="n">
-        <v>91826</v>
+        <v>79643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3100</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665842</v>
+        <v>665631</v>
       </c>
       <c r="R10" t="n">
-        <v>7185565</v>
+        <v>7185482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,6 +1586,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1602,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880461</v>
+        <v>119880455</v>
       </c>
       <c r="B11" t="n">
-        <v>91844</v>
+        <v>89275</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1633,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665905</v>
+        <v>665872</v>
       </c>
       <c r="R11" t="n">
-        <v>7185598</v>
+        <v>7185555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880454</v>
+        <v>119880424</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665867</v>
+        <v>665577</v>
       </c>
       <c r="R13" t="n">
-        <v>7185544</v>
+        <v>7185596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880409</v>
+        <v>119880414</v>
       </c>
       <c r="B14" t="n">
-        <v>89230</v>
+        <v>78171</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1596</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665652</v>
+        <v>665625</v>
       </c>
       <c r="R14" t="n">
-        <v>7185701</v>
+        <v>7185661</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880473</v>
+        <v>119880471</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>91828</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2037,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>149</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666000</v>
+        <v>665988</v>
       </c>
       <c r="R15" t="n">
-        <v>7185668</v>
+        <v>7185667</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880459</v>
+        <v>119880447</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2143,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665913</v>
+        <v>665779</v>
       </c>
       <c r="R16" t="n">
-        <v>7185574</v>
+        <v>7185591</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880439</v>
+        <v>119880461</v>
       </c>
       <c r="B17" t="n">
-        <v>89633</v>
+        <v>91844</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2241,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665731</v>
+        <v>665905</v>
       </c>
       <c r="R17" t="n">
-        <v>7185521</v>
+        <v>7185598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880425</v>
+        <v>119880418</v>
       </c>
       <c r="B18" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2343,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665574</v>
+        <v>665618</v>
       </c>
       <c r="R18" t="n">
-        <v>7185592</v>
+        <v>7185647</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880438</v>
+        <v>119880472</v>
       </c>
       <c r="B19" t="n">
-        <v>91844</v>
+        <v>91826</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,25 +2445,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665723</v>
+        <v>665998</v>
       </c>
       <c r="R19" t="n">
-        <v>7185514</v>
+        <v>7185666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,17 +2528,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880419</v>
+        <v>119880410</v>
       </c>
       <c r="B20" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2551,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665600</v>
+        <v>665646</v>
       </c>
       <c r="R20" t="n">
-        <v>7185629</v>
+        <v>7185686</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880433</v>
+        <v>119880440</v>
       </c>
       <c r="B21" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2653,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2677,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665516</v>
+        <v>665733</v>
       </c>
       <c r="R21" t="n">
-        <v>7185504</v>
+        <v>7185520</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880467</v>
+        <v>119880452</v>
       </c>
       <c r="B22" t="n">
-        <v>89252</v>
+        <v>91826</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2751,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665967</v>
+        <v>665842</v>
       </c>
       <c r="R22" t="n">
-        <v>7185660</v>
+        <v>7185565</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880468</v>
+        <v>119880442</v>
       </c>
       <c r="B23" t="n">
-        <v>79144</v>
+        <v>91834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2857,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665975</v>
+        <v>665744</v>
       </c>
       <c r="R23" t="n">
-        <v>7185666</v>
+        <v>7185572</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880457</v>
+        <v>119880398</v>
       </c>
       <c r="B24" t="n">
-        <v>91852</v>
+        <v>89275</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,25 +2955,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665871</v>
+        <v>665837</v>
       </c>
       <c r="R24" t="n">
-        <v>7185570</v>
+        <v>7185742</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880443</v>
+        <v>119880430</v>
       </c>
       <c r="B25" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3057,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665746</v>
+        <v>665527</v>
       </c>
       <c r="R25" t="n">
-        <v>7185579</v>
+        <v>7185533</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880412</v>
+        <v>119880409</v>
       </c>
       <c r="B26" t="n">
-        <v>78171</v>
+        <v>89230</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3159,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>1596</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665642</v>
+        <v>665652</v>
       </c>
       <c r="R26" t="n">
-        <v>7185682</v>
+        <v>7185701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,7 +3249,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880431</v>
+        <v>119880412</v>
       </c>
       <c r="B27" t="n">
         <v>78171</v>
@@ -3274,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665509</v>
+        <v>665642</v>
       </c>
       <c r="R27" t="n">
-        <v>7185520</v>
+        <v>7185682</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880453</v>
+        <v>119880441</v>
       </c>
       <c r="B28" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665867</v>
+        <v>665740</v>
       </c>
       <c r="R28" t="n">
-        <v>7185548</v>
+        <v>7185522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880429</v>
+        <v>119880433</v>
       </c>
       <c r="B29" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3454,21 +3469,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3493,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665527</v>
+        <v>665516</v>
       </c>
       <c r="R29" t="n">
-        <v>7185533</v>
+        <v>7185504</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880418</v>
+        <v>119880423</v>
       </c>
       <c r="B30" t="n">
-        <v>91852</v>
+        <v>78263</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,25 +3567,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3595,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665618</v>
+        <v>665584</v>
       </c>
       <c r="R30" t="n">
-        <v>7185647</v>
+        <v>7185605</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880442</v>
+        <v>119880446</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3673,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665744</v>
+        <v>665779</v>
       </c>
       <c r="R31" t="n">
-        <v>7185572</v>
+        <v>7185598</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880423</v>
+        <v>119880456</v>
       </c>
       <c r="B32" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3760,21 +3775,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665584</v>
+        <v>665872</v>
       </c>
       <c r="R32" t="n">
-        <v>7185605</v>
+        <v>7185563</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880462</v>
+        <v>119880468</v>
       </c>
       <c r="B33" t="n">
-        <v>89252</v>
+        <v>79144</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,25 +3873,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665918</v>
+        <v>665975</v>
       </c>
       <c r="R33" t="n">
-        <v>7185620</v>
+        <v>7185666</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880441</v>
+        <v>119880443</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3960,25 +3975,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665740</v>
+        <v>665746</v>
       </c>
       <c r="R34" t="n">
-        <v>7185522</v>
+        <v>7185579</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4065,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880430</v>
+        <v>119880439</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4066,21 +4081,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665527</v>
+        <v>665731</v>
       </c>
       <c r="R35" t="n">
-        <v>7185533</v>
+        <v>7185521</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880424</v>
+        <v>119880429</v>
       </c>
       <c r="B36" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4183,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665577</v>
+        <v>665527</v>
       </c>
       <c r="R36" t="n">
-        <v>7185596</v>
+        <v>7185533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4254,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880447</v>
+        <v>119880454</v>
       </c>
       <c r="B37" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4270,21 +4285,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4294,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665779</v>
+        <v>665867</v>
       </c>
       <c r="R37" t="n">
-        <v>7185591</v>
+        <v>7185544</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4356,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880472</v>
+        <v>119880428</v>
       </c>
       <c r="B38" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4372,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665998</v>
+        <v>665530</v>
       </c>
       <c r="R38" t="n">
-        <v>7185666</v>
+        <v>7185543</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880437</v>
+        <v>119880463</v>
       </c>
       <c r="B39" t="n">
-        <v>79643</v>
+        <v>91826</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4470,25 +4485,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>3100</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,10 +4513,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665631</v>
+        <v>665918</v>
       </c>
       <c r="R39" t="n">
-        <v>7185482</v>
+        <v>7185620</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4544,21 +4559,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880446</v>
+        <v>119880417</v>
       </c>
       <c r="B40" t="n">
-        <v>78171</v>
+        <v>77458</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4591,21 +4591,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665779</v>
+        <v>665632</v>
       </c>
       <c r="R40" t="n">
-        <v>7185598</v>
+        <v>7185649</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880427</v>
+        <v>119880451</v>
       </c>
       <c r="B41" t="n">
         <v>78171</v>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665573</v>
+        <v>665824</v>
       </c>
       <c r="R41" t="n">
-        <v>7185584</v>
+        <v>7185574</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880463</v>
+        <v>119880466</v>
       </c>
       <c r="B42" t="n">
-        <v>91826</v>
+        <v>91832</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665918</v>
+        <v>665966</v>
       </c>
       <c r="R42" t="n">
-        <v>7185620</v>
+        <v>7185634</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880448</v>
+        <v>119880453</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665801</v>
+        <v>665867</v>
       </c>
       <c r="R43" t="n">
-        <v>7185555</v>
+        <v>7185548</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880428</v>
+        <v>119880413</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +4995,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665530</v>
+        <v>665629</v>
       </c>
       <c r="R44" t="n">
-        <v>7185543</v>
+        <v>7185671</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880456</v>
+        <v>119880470</v>
       </c>
       <c r="B45" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,25 +5097,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665872</v>
+        <v>665982</v>
       </c>
       <c r="R45" t="n">
-        <v>7185563</v>
+        <v>7185672</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880455</v>
+        <v>119880425</v>
       </c>
       <c r="B46" t="n">
-        <v>89275</v>
+        <v>89633</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,25 +5199,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6286</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665872</v>
+        <v>665574</v>
       </c>
       <c r="R46" t="n">
-        <v>7185555</v>
+        <v>7185592</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880466</v>
+        <v>119880448</v>
       </c>
       <c r="B47" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665966</v>
+        <v>665801</v>
       </c>
       <c r="R47" t="n">
-        <v>7185634</v>
+        <v>7185555</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,7 +5391,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880440</v>
+        <v>119880459</v>
       </c>
       <c r="B48" t="n">
         <v>78171</v>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665733</v>
+        <v>665913</v>
       </c>
       <c r="R48" t="n">
-        <v>7185520</v>
+        <v>7185574</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880411</v>
+        <v>119880444</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,25 +5505,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665645</v>
+        <v>665746</v>
       </c>
       <c r="R49" t="n">
-        <v>7185685</v>
+        <v>7185579</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880413</v>
+        <v>119880445</v>
       </c>
       <c r="B50" t="n">
-        <v>89275</v>
+        <v>78171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,25 +5607,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665629</v>
+        <v>665752</v>
       </c>
       <c r="R50" t="n">
-        <v>7185671</v>
+        <v>7185584</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880445</v>
+        <v>119880419</v>
       </c>
       <c r="B51" t="n">
         <v>78171</v>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665752</v>
+        <v>665600</v>
       </c>
       <c r="R51" t="n">
-        <v>7185584</v>
+        <v>7185629</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880414</v>
+        <v>119880467</v>
       </c>
       <c r="B52" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,25 +5811,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665625</v>
+        <v>665967</v>
       </c>
       <c r="R52" t="n">
-        <v>7185661</v>
+        <v>7185660</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880450</v>
+        <v>119880411</v>
       </c>
       <c r="B53" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665811</v>
+        <v>665645</v>
       </c>
       <c r="R53" t="n">
-        <v>7185566</v>
+        <v>7185685</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880417</v>
+        <v>119880473</v>
       </c>
       <c r="B54" t="n">
-        <v>77458</v>
+        <v>91852</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6487</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665632</v>
+        <v>666000</v>
       </c>
       <c r="R54" t="n">
-        <v>7185649</v>
+        <v>7185668</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6098,17 +6098,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880464</v>
+        <v>119880427</v>
       </c>
       <c r="B55" t="n">
-        <v>91852</v>
+        <v>78171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6117,25 +6117,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665922</v>
+        <v>665573</v>
       </c>
       <c r="R55" t="n">
-        <v>7185624</v>
+        <v>7185584</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880449</v>
+        <v>119880438</v>
       </c>
       <c r="B56" t="n">
-        <v>78171</v>
+        <v>91844</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6219,25 +6219,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665811</v>
+        <v>665723</v>
       </c>
       <c r="R56" t="n">
-        <v>7185566</v>
+        <v>7185514</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880458</v>
+        <v>119880465</v>
       </c>
       <c r="B57" t="n">
-        <v>89252</v>
+        <v>91828</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665911</v>
+        <v>665944</v>
       </c>
       <c r="R57" t="n">
-        <v>7185565</v>
+        <v>7185632</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -2943,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880398</v>
+        <v>119880430</v>
       </c>
       <c r="B24" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,25 +2955,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665837</v>
+        <v>665527</v>
       </c>
       <c r="R24" t="n">
-        <v>7185742</v>
+        <v>7185533</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880430</v>
+        <v>119880398</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,25 +3057,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665527</v>
+        <v>665837</v>
       </c>
       <c r="R25" t="n">
-        <v>7185533</v>
+        <v>7185742</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880466</v>
+        <v>119880413</v>
       </c>
       <c r="B42" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665966</v>
+        <v>665629</v>
       </c>
       <c r="R42" t="n">
-        <v>7185634</v>
+        <v>7185671</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880453</v>
+        <v>119880470</v>
       </c>
       <c r="B43" t="n">
-        <v>91826</v>
+        <v>89252</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,25 +4893,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665867</v>
+        <v>665982</v>
       </c>
       <c r="R43" t="n">
-        <v>7185548</v>
+        <v>7185672</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880413</v>
+        <v>119880466</v>
       </c>
       <c r="B44" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +4995,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665629</v>
+        <v>665966</v>
       </c>
       <c r="R44" t="n">
-        <v>7185671</v>
+        <v>7185634</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880470</v>
+        <v>119880453</v>
       </c>
       <c r="B45" t="n">
-        <v>89252</v>
+        <v>91826</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,25 +5097,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665982</v>
+        <v>665867</v>
       </c>
       <c r="R45" t="n">
-        <v>7185672</v>
+        <v>7185548</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880458</v>
+        <v>119880410</v>
       </c>
       <c r="B3" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665911</v>
+        <v>665646</v>
       </c>
       <c r="R3" t="n">
-        <v>7185565</v>
+        <v>7185686</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880449</v>
+        <v>119880465</v>
       </c>
       <c r="B4" t="n">
-        <v>78171</v>
+        <v>91828</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665811</v>
+        <v>665944</v>
       </c>
       <c r="R4" t="n">
-        <v>7185566</v>
+        <v>7185632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880450</v>
+        <v>119880412</v>
       </c>
       <c r="B5" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665811</v>
+        <v>665642</v>
       </c>
       <c r="R5" t="n">
-        <v>7185566</v>
+        <v>7185682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880457</v>
+        <v>119880468</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>79144</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665871</v>
+        <v>665975</v>
       </c>
       <c r="R6" t="n">
-        <v>7185570</v>
+        <v>7185666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880464</v>
+        <v>119880431</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>78171</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665922</v>
+        <v>665509</v>
       </c>
       <c r="R7" t="n">
-        <v>7185624</v>
+        <v>7185520</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880462</v>
+        <v>119880461</v>
       </c>
       <c r="B8" t="n">
-        <v>89252</v>
+        <v>91844</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665918</v>
+        <v>665905</v>
       </c>
       <c r="R8" t="n">
-        <v>7185620</v>
+        <v>7185598</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880431</v>
+        <v>119880438</v>
       </c>
       <c r="B9" t="n">
-        <v>78171</v>
+        <v>91844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665509</v>
+        <v>665723</v>
       </c>
       <c r="R9" t="n">
-        <v>7185520</v>
+        <v>7185514</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880437</v>
+        <v>119880423</v>
       </c>
       <c r="B10" t="n">
-        <v>79643</v>
+        <v>78263</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665631</v>
+        <v>665584</v>
       </c>
       <c r="R10" t="n">
-        <v>7185482</v>
+        <v>7185605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,21 +1586,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1617,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880455</v>
+        <v>119880440</v>
       </c>
       <c r="B11" t="n">
-        <v>89275</v>
+        <v>78171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665872</v>
+        <v>665733</v>
       </c>
       <c r="R11" t="n">
-        <v>7185555</v>
+        <v>7185520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880460</v>
+        <v>119880457</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665910</v>
+        <v>665871</v>
       </c>
       <c r="R12" t="n">
-        <v>7185584</v>
+        <v>7185570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880424</v>
+        <v>119880464</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665577</v>
+        <v>665922</v>
       </c>
       <c r="R13" t="n">
-        <v>7185596</v>
+        <v>7185624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880414</v>
+        <v>119880458</v>
       </c>
       <c r="B14" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665625</v>
+        <v>665911</v>
       </c>
       <c r="R14" t="n">
-        <v>7185661</v>
+        <v>7185565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880471</v>
+        <v>119880454</v>
       </c>
       <c r="B15" t="n">
-        <v>91828</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665988</v>
+        <v>665867</v>
       </c>
       <c r="R15" t="n">
-        <v>7185667</v>
+        <v>7185544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880447</v>
+        <v>119880467</v>
       </c>
       <c r="B16" t="n">
-        <v>91856</v>
+        <v>89252</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665779</v>
+        <v>665967</v>
       </c>
       <c r="R16" t="n">
-        <v>7185591</v>
+        <v>7185660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880461</v>
+        <v>119880456</v>
       </c>
       <c r="B17" t="n">
-        <v>91844</v>
+        <v>78171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665905</v>
+        <v>665872</v>
       </c>
       <c r="R17" t="n">
-        <v>7185598</v>
+        <v>7185563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880418</v>
+        <v>119880459</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>78171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665618</v>
+        <v>665913</v>
       </c>
       <c r="R18" t="n">
-        <v>7185647</v>
+        <v>7185574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880472</v>
+        <v>119880425</v>
       </c>
       <c r="B19" t="n">
-        <v>91826</v>
+        <v>89633</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3100</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665998</v>
+        <v>665574</v>
       </c>
       <c r="R19" t="n">
-        <v>7185666</v>
+        <v>7185592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,17 +2513,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Emil Larsson</t>
+          <t>Emil Larsson, Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880410</v>
+        <v>119880444</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>89633</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2551,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665646</v>
+        <v>665746</v>
       </c>
       <c r="R20" t="n">
-        <v>7185686</v>
+        <v>7185579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880440</v>
+        <v>119880411</v>
       </c>
       <c r="B21" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2677,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665733</v>
+        <v>665645</v>
       </c>
       <c r="R21" t="n">
-        <v>7185520</v>
+        <v>7185685</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880452</v>
+        <v>119880398</v>
       </c>
       <c r="B22" t="n">
-        <v>91826</v>
+        <v>89275</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3100</v>
+        <v>6286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665842</v>
+        <v>665837</v>
       </c>
       <c r="R22" t="n">
-        <v>7185565</v>
+        <v>7185742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880442</v>
+        <v>119880413</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>89275</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,25 +2838,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2881,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665744</v>
+        <v>665629</v>
       </c>
       <c r="R23" t="n">
-        <v>7185572</v>
+        <v>7185671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3045,7 +3030,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880398</v>
+        <v>119880455</v>
       </c>
       <c r="B25" t="n">
         <v>89275</v>
@@ -3085,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665837</v>
+        <v>665872</v>
       </c>
       <c r="R25" t="n">
-        <v>7185742</v>
+        <v>7185555</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880409</v>
+        <v>119880424</v>
       </c>
       <c r="B26" t="n">
-        <v>89230</v>
+        <v>91834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,25 +3144,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665652</v>
+        <v>665577</v>
       </c>
       <c r="R26" t="n">
-        <v>7185701</v>
+        <v>7185596</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880412</v>
+        <v>119880439</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>89633</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665642</v>
+        <v>665731</v>
       </c>
       <c r="R27" t="n">
-        <v>7185682</v>
+        <v>7185521</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880441</v>
+        <v>119880473</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3391,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665740</v>
+        <v>666000</v>
       </c>
       <c r="R28" t="n">
-        <v>7185522</v>
+        <v>7185668</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880433</v>
+        <v>119880451</v>
       </c>
       <c r="B29" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3469,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3493,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665516</v>
+        <v>665824</v>
       </c>
       <c r="R29" t="n">
-        <v>7185504</v>
+        <v>7185574</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3555,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880423</v>
+        <v>119880437</v>
       </c>
       <c r="B30" t="n">
-        <v>78263</v>
+        <v>79643</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,25 +3552,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3595,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665584</v>
+        <v>665631</v>
       </c>
       <c r="R30" t="n">
-        <v>7185605</v>
+        <v>7185482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3641,6 +3626,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3657,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880446</v>
+        <v>119880453</v>
       </c>
       <c r="B31" t="n">
-        <v>78171</v>
+        <v>91826</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,21 +3673,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665779</v>
+        <v>665867</v>
       </c>
       <c r="R31" t="n">
-        <v>7185598</v>
+        <v>7185548</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880456</v>
+        <v>119880442</v>
       </c>
       <c r="B32" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665872</v>
+        <v>665744</v>
       </c>
       <c r="R32" t="n">
-        <v>7185563</v>
+        <v>7185572</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880468</v>
+        <v>119880452</v>
       </c>
       <c r="B33" t="n">
-        <v>79144</v>
+        <v>91826</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665975</v>
+        <v>665842</v>
       </c>
       <c r="R33" t="n">
-        <v>7185666</v>
+        <v>7185565</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880443</v>
+        <v>119880429</v>
       </c>
       <c r="B34" t="n">
-        <v>91852</v>
+        <v>91883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3975,25 +3975,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665746</v>
+        <v>665527</v>
       </c>
       <c r="R34" t="n">
-        <v>7185579</v>
+        <v>7185533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880439</v>
+        <v>119880448</v>
       </c>
       <c r="B35" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,21 +4081,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665731</v>
+        <v>665801</v>
       </c>
       <c r="R35" t="n">
-        <v>7185521</v>
+        <v>7185555</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880429</v>
+        <v>119880433</v>
       </c>
       <c r="B36" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665527</v>
+        <v>665516</v>
       </c>
       <c r="R36" t="n">
-        <v>7185533</v>
+        <v>7185504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880454</v>
+        <v>119880471</v>
       </c>
       <c r="B37" t="n">
-        <v>91832</v>
+        <v>91828</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665867</v>
+        <v>665988</v>
       </c>
       <c r="R37" t="n">
-        <v>7185544</v>
+        <v>7185667</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880428</v>
+        <v>119880446</v>
       </c>
       <c r="B38" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665530</v>
+        <v>665779</v>
       </c>
       <c r="R38" t="n">
-        <v>7185543</v>
+        <v>7185598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880463</v>
+        <v>119880445</v>
       </c>
       <c r="B39" t="n">
-        <v>91826</v>
+        <v>78171</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665918</v>
+        <v>665752</v>
       </c>
       <c r="R39" t="n">
-        <v>7185620</v>
+        <v>7185584</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880417</v>
+        <v>119880418</v>
       </c>
       <c r="B40" t="n">
-        <v>77458</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,25 +4587,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665632</v>
+        <v>665618</v>
       </c>
       <c r="R40" t="n">
-        <v>7185649</v>
+        <v>7185647</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880451</v>
+        <v>119880409</v>
       </c>
       <c r="B41" t="n">
-        <v>78171</v>
+        <v>89230</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,25 +4689,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>1596</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665824</v>
+        <v>665652</v>
       </c>
       <c r="R41" t="n">
-        <v>7185574</v>
+        <v>7185701</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880413</v>
+        <v>119880472</v>
       </c>
       <c r="B42" t="n">
-        <v>89275</v>
+        <v>91826</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6286</v>
+        <v>3100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665629</v>
+        <v>665998</v>
       </c>
       <c r="R42" t="n">
-        <v>7185671</v>
+        <v>7185666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880470</v>
+        <v>119880419</v>
       </c>
       <c r="B43" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,25 +4893,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665982</v>
+        <v>665600</v>
       </c>
       <c r="R43" t="n">
-        <v>7185672</v>
+        <v>7185629</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880466</v>
+        <v>119880470</v>
       </c>
       <c r="B44" t="n">
-        <v>91832</v>
+        <v>89252</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +4995,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665966</v>
+        <v>665982</v>
       </c>
       <c r="R44" t="n">
-        <v>7185634</v>
+        <v>7185672</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880453</v>
+        <v>119880428</v>
       </c>
       <c r="B45" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,21 +5101,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665867</v>
+        <v>665530</v>
       </c>
       <c r="R45" t="n">
-        <v>7185548</v>
+        <v>7185543</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880425</v>
+        <v>119880462</v>
       </c>
       <c r="B46" t="n">
-        <v>89633</v>
+        <v>89252</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,25 +5199,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>6276</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665574</v>
+        <v>665918</v>
       </c>
       <c r="R46" t="n">
-        <v>7185592</v>
+        <v>7185620</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880448</v>
+        <v>119880449</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665801</v>
+        <v>665811</v>
       </c>
       <c r="R47" t="n">
-        <v>7185555</v>
+        <v>7185566</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,7 +5391,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880459</v>
+        <v>119880427</v>
       </c>
       <c r="B48" t="n">
         <v>78171</v>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665913</v>
+        <v>665573</v>
       </c>
       <c r="R48" t="n">
-        <v>7185574</v>
+        <v>7185584</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880444</v>
+        <v>119880414</v>
       </c>
       <c r="B49" t="n">
-        <v>89633</v>
+        <v>78171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665746</v>
+        <v>665625</v>
       </c>
       <c r="R49" t="n">
-        <v>7185579</v>
+        <v>7185661</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880445</v>
+        <v>119880466</v>
       </c>
       <c r="B50" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,21 +5611,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665752</v>
+        <v>665966</v>
       </c>
       <c r="R50" t="n">
-        <v>7185584</v>
+        <v>7185634</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880419</v>
+        <v>119880450</v>
       </c>
       <c r="B51" t="n">
-        <v>78171</v>
+        <v>89633</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665600</v>
+        <v>665811</v>
       </c>
       <c r="R51" t="n">
-        <v>7185629</v>
+        <v>7185566</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880467</v>
+        <v>119880463</v>
       </c>
       <c r="B52" t="n">
-        <v>89252</v>
+        <v>91826</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,25 +5811,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665967</v>
+        <v>665918</v>
       </c>
       <c r="R52" t="n">
-        <v>7185660</v>
+        <v>7185620</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880411</v>
+        <v>119880441</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665645</v>
+        <v>665740</v>
       </c>
       <c r="R53" t="n">
-        <v>7185685</v>
+        <v>7185522</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880473</v>
+        <v>119880443</v>
       </c>
       <c r="B54" t="n">
         <v>91852</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>666000</v>
+        <v>665746</v>
       </c>
       <c r="R54" t="n">
-        <v>7185668</v>
+        <v>7185579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6098,17 +6098,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Magnus Wadstein, Emil Larsson</t>
+          <t>Emil Larsson, Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880427</v>
+        <v>119880460</v>
       </c>
       <c r="B55" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6121,21 +6121,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665573</v>
+        <v>665910</v>
       </c>
       <c r="R55" t="n">
         <v>7185584</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880438</v>
+        <v>119880447</v>
       </c>
       <c r="B56" t="n">
-        <v>91844</v>
+        <v>91856</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6219,25 +6219,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665723</v>
+        <v>665779</v>
       </c>
       <c r="R56" t="n">
-        <v>7185514</v>
+        <v>7185591</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880465</v>
+        <v>119880417</v>
       </c>
       <c r="B57" t="n">
-        <v>91828</v>
+        <v>77458</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6321,25 +6321,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>149</v>
+        <v>6487</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665944</v>
+        <v>665632</v>
       </c>
       <c r="R57" t="n">
-        <v>7185632</v>
+        <v>7185649</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880454</v>
+        <v>119880456</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665867</v>
+        <v>665872</v>
       </c>
       <c r="R15" t="n">
-        <v>7185544</v>
+        <v>7185563</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880467</v>
+        <v>119880459</v>
       </c>
       <c r="B16" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665967</v>
+        <v>665913</v>
       </c>
       <c r="R16" t="n">
-        <v>7185660</v>
+        <v>7185574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880456</v>
+        <v>119880467</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665872</v>
+        <v>665967</v>
       </c>
       <c r="R17" t="n">
-        <v>7185563</v>
+        <v>7185660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880459</v>
+        <v>119880454</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665913</v>
+        <v>665867</v>
       </c>
       <c r="R18" t="n">
-        <v>7185574</v>
+        <v>7185544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880398</v>
+        <v>119880430</v>
       </c>
       <c r="B22" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665837</v>
+        <v>665527</v>
       </c>
       <c r="R22" t="n">
-        <v>7185742</v>
+        <v>7185533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880413</v>
+        <v>119880398</v>
       </c>
       <c r="B23" t="n">
         <v>89275</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665629</v>
+        <v>665837</v>
       </c>
       <c r="R23" t="n">
-        <v>7185671</v>
+        <v>7185742</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880430</v>
+        <v>119880413</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665527</v>
+        <v>665629</v>
       </c>
       <c r="R24" t="n">
-        <v>7185533</v>
+        <v>7185671</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880437</v>
+        <v>119880453</v>
       </c>
       <c r="B30" t="n">
-        <v>79643</v>
+        <v>91826</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,25 +3552,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665631</v>
+        <v>665867</v>
       </c>
       <c r="R30" t="n">
-        <v>7185482</v>
+        <v>7185548</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,21 +3626,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3657,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880453</v>
+        <v>119880442</v>
       </c>
       <c r="B31" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,21 +3658,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665867</v>
+        <v>665744</v>
       </c>
       <c r="R31" t="n">
-        <v>7185548</v>
+        <v>7185572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880442</v>
+        <v>119880437</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>79643</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,25 +3756,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665744</v>
+        <v>665631</v>
       </c>
       <c r="R32" t="n">
-        <v>7185572</v>
+        <v>7185482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3845,6 +3830,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880433</v>
+        <v>119880471</v>
       </c>
       <c r="B36" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,25 +4179,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665516</v>
+        <v>665988</v>
       </c>
       <c r="R36" t="n">
-        <v>7185504</v>
+        <v>7185667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880471</v>
+        <v>119880446</v>
       </c>
       <c r="B37" t="n">
-        <v>91828</v>
+        <v>78171</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665988</v>
+        <v>665779</v>
       </c>
       <c r="R37" t="n">
-        <v>7185667</v>
+        <v>7185598</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880446</v>
+        <v>119880433</v>
       </c>
       <c r="B38" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665779</v>
+        <v>665516</v>
       </c>
       <c r="R38" t="n">
-        <v>7185598</v>
+        <v>7185504</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880418</v>
+        <v>119880409</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>89230</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,25 +4587,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>1596</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665618</v>
+        <v>665652</v>
       </c>
       <c r="R40" t="n">
-        <v>7185647</v>
+        <v>7185701</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880409</v>
+        <v>119880418</v>
       </c>
       <c r="B41" t="n">
-        <v>89230</v>
+        <v>91852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,25 +4689,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1596</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665652</v>
+        <v>665618</v>
       </c>
       <c r="R41" t="n">
-        <v>7185701</v>
+        <v>7185647</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880472</v>
+        <v>119880470</v>
       </c>
       <c r="B42" t="n">
-        <v>91826</v>
+        <v>89252</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665998</v>
+        <v>665982</v>
       </c>
       <c r="R42" t="n">
-        <v>7185666</v>
+        <v>7185672</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880419</v>
+        <v>119880428</v>
       </c>
       <c r="B43" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665600</v>
+        <v>665530</v>
       </c>
       <c r="R43" t="n">
-        <v>7185629</v>
+        <v>7185543</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880470</v>
+        <v>119880419</v>
       </c>
       <c r="B44" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +4995,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665982</v>
+        <v>665600</v>
       </c>
       <c r="R44" t="n">
-        <v>7185672</v>
+        <v>7185629</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880428</v>
+        <v>119880472</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>91826</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,21 +5101,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665530</v>
+        <v>665998</v>
       </c>
       <c r="R45" t="n">
-        <v>7185543</v>
+        <v>7185666</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880449</v>
+        <v>119880466</v>
       </c>
       <c r="B47" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665811</v>
+        <v>665966</v>
       </c>
       <c r="R47" t="n">
-        <v>7185566</v>
+        <v>7185634</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,7 +5391,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880427</v>
+        <v>119880449</v>
       </c>
       <c r="B48" t="n">
         <v>78171</v>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665573</v>
+        <v>665811</v>
       </c>
       <c r="R48" t="n">
-        <v>7185584</v>
+        <v>7185566</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880414</v>
+        <v>119880427</v>
       </c>
       <c r="B49" t="n">
         <v>78171</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665625</v>
+        <v>665573</v>
       </c>
       <c r="R49" t="n">
-        <v>7185661</v>
+        <v>7185584</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880466</v>
+        <v>119880414</v>
       </c>
       <c r="B50" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,21 +5611,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665966</v>
+        <v>665625</v>
       </c>
       <c r="R50" t="n">
-        <v>7185634</v>
+        <v>7185661</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880447</v>
+        <v>119880417</v>
       </c>
       <c r="B56" t="n">
-        <v>91856</v>
+        <v>77458</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2059</v>
+        <v>6487</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665779</v>
+        <v>665632</v>
       </c>
       <c r="R56" t="n">
-        <v>7185591</v>
+        <v>7185649</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880417</v>
+        <v>119880447</v>
       </c>
       <c r="B57" t="n">
-        <v>77458</v>
+        <v>91856</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6487</v>
+        <v>2059</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665632</v>
+        <v>665779</v>
       </c>
       <c r="R57" t="n">
-        <v>7185649</v>
+        <v>7185591</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880456</v>
+        <v>119880454</v>
       </c>
       <c r="B15" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665872</v>
+        <v>665867</v>
       </c>
       <c r="R15" t="n">
-        <v>7185563</v>
+        <v>7185544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880459</v>
+        <v>119880467</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665913</v>
+        <v>665967</v>
       </c>
       <c r="R16" t="n">
-        <v>7185574</v>
+        <v>7185660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880467</v>
+        <v>119880456</v>
       </c>
       <c r="B17" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665967</v>
+        <v>665872</v>
       </c>
       <c r="R17" t="n">
-        <v>7185660</v>
+        <v>7185563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880454</v>
+        <v>119880459</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665867</v>
+        <v>665913</v>
       </c>
       <c r="R18" t="n">
-        <v>7185544</v>
+        <v>7185574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880430</v>
+        <v>119880398</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665527</v>
+        <v>665837</v>
       </c>
       <c r="R22" t="n">
-        <v>7185533</v>
+        <v>7185742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880398</v>
+        <v>119880413</v>
       </c>
       <c r="B23" t="n">
         <v>89275</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665837</v>
+        <v>665629</v>
       </c>
       <c r="R23" t="n">
-        <v>7185742</v>
+        <v>7185671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880413</v>
+        <v>119880430</v>
       </c>
       <c r="B24" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665629</v>
+        <v>665527</v>
       </c>
       <c r="R24" t="n">
-        <v>7185671</v>
+        <v>7185533</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880424</v>
+        <v>119880439</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665577</v>
+        <v>665731</v>
       </c>
       <c r="R26" t="n">
-        <v>7185596</v>
+        <v>7185521</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880439</v>
+        <v>119880473</v>
       </c>
       <c r="B27" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3246,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665731</v>
+        <v>666000</v>
       </c>
       <c r="R27" t="n">
-        <v>7185521</v>
+        <v>7185668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880473</v>
+        <v>119880424</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>666000</v>
+        <v>665577</v>
       </c>
       <c r="R28" t="n">
-        <v>7185668</v>
+        <v>7185596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880453</v>
+        <v>119880437</v>
       </c>
       <c r="B30" t="n">
-        <v>91826</v>
+        <v>79643</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,25 +3552,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665867</v>
+        <v>665631</v>
       </c>
       <c r="R30" t="n">
-        <v>7185548</v>
+        <v>7185482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,6 +3626,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3642,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880442</v>
+        <v>119880453</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3658,21 +3673,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665744</v>
+        <v>665867</v>
       </c>
       <c r="R31" t="n">
-        <v>7185572</v>
+        <v>7185548</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880437</v>
+        <v>119880442</v>
       </c>
       <c r="B32" t="n">
-        <v>79643</v>
+        <v>91834</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,25 +3771,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665631</v>
+        <v>665744</v>
       </c>
       <c r="R32" t="n">
-        <v>7185482</v>
+        <v>7185572</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3830,21 +3845,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880471</v>
+        <v>119880433</v>
       </c>
       <c r="B36" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,25 +4179,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665988</v>
+        <v>665516</v>
       </c>
       <c r="R36" t="n">
-        <v>7185667</v>
+        <v>7185504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880446</v>
+        <v>119880471</v>
       </c>
       <c r="B37" t="n">
-        <v>78171</v>
+        <v>91828</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665779</v>
+        <v>665988</v>
       </c>
       <c r="R37" t="n">
-        <v>7185598</v>
+        <v>7185667</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880433</v>
+        <v>119880446</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665516</v>
+        <v>665779</v>
       </c>
       <c r="R38" t="n">
-        <v>7185504</v>
+        <v>7185598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880470</v>
+        <v>119880472</v>
       </c>
       <c r="B42" t="n">
-        <v>89252</v>
+        <v>91826</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6276</v>
+        <v>3100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665982</v>
+        <v>665998</v>
       </c>
       <c r="R42" t="n">
-        <v>7185672</v>
+        <v>7185666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880428</v>
+        <v>119880419</v>
       </c>
       <c r="B43" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665530</v>
+        <v>665600</v>
       </c>
       <c r="R43" t="n">
-        <v>7185543</v>
+        <v>7185629</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880419</v>
+        <v>119880470</v>
       </c>
       <c r="B44" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +4995,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665600</v>
+        <v>665982</v>
       </c>
       <c r="R44" t="n">
-        <v>7185629</v>
+        <v>7185672</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880472</v>
+        <v>119880428</v>
       </c>
       <c r="B45" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,21 +5101,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665998</v>
+        <v>665530</v>
       </c>
       <c r="R45" t="n">
-        <v>7185666</v>
+        <v>7185543</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880466</v>
+        <v>119880449</v>
       </c>
       <c r="B47" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5305,21 +5305,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665966</v>
+        <v>665811</v>
       </c>
       <c r="R47" t="n">
-        <v>7185634</v>
+        <v>7185566</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,7 +5391,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880449</v>
+        <v>119880427</v>
       </c>
       <c r="B48" t="n">
         <v>78171</v>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665811</v>
+        <v>665573</v>
       </c>
       <c r="R48" t="n">
-        <v>7185566</v>
+        <v>7185584</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,7 +5493,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880427</v>
+        <v>119880414</v>
       </c>
       <c r="B49" t="n">
         <v>78171</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665573</v>
+        <v>665625</v>
       </c>
       <c r="R49" t="n">
-        <v>7185584</v>
+        <v>7185661</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880414</v>
+        <v>119880466</v>
       </c>
       <c r="B50" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,21 +5611,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665625</v>
+        <v>665966</v>
       </c>
       <c r="R50" t="n">
-        <v>7185661</v>
+        <v>7185634</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880463</v>
+        <v>119880441</v>
       </c>
       <c r="B52" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665918</v>
+        <v>665740</v>
       </c>
       <c r="R52" t="n">
-        <v>7185620</v>
+        <v>7185522</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880441</v>
+        <v>119880443</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665740</v>
+        <v>665746</v>
       </c>
       <c r="R53" t="n">
-        <v>7185522</v>
+        <v>7185579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880443</v>
+        <v>119880463</v>
       </c>
       <c r="B54" t="n">
-        <v>91852</v>
+        <v>91826</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665746</v>
+        <v>665918</v>
       </c>
       <c r="R54" t="n">
-        <v>7185579</v>
+        <v>7185620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880457</v>
+        <v>119880458</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>89252</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665871</v>
+        <v>665911</v>
       </c>
       <c r="R12" t="n">
-        <v>7185570</v>
+        <v>7185565</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880464</v>
+        <v>119880457</v>
       </c>
       <c r="B13" t="n">
         <v>91852</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665922</v>
+        <v>665871</v>
       </c>
       <c r="R13" t="n">
-        <v>7185624</v>
+        <v>7185570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880458</v>
+        <v>119880464</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665911</v>
+        <v>665922</v>
       </c>
       <c r="R14" t="n">
-        <v>7185565</v>
+        <v>7185624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880454</v>
+        <v>119880456</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665867</v>
+        <v>665872</v>
       </c>
       <c r="R15" t="n">
-        <v>7185544</v>
+        <v>7185563</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880467</v>
+        <v>119880459</v>
       </c>
       <c r="B16" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665967</v>
+        <v>665913</v>
       </c>
       <c r="R16" t="n">
-        <v>7185660</v>
+        <v>7185574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880456</v>
+        <v>119880467</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665872</v>
+        <v>665967</v>
       </c>
       <c r="R17" t="n">
-        <v>7185563</v>
+        <v>7185660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880459</v>
+        <v>119880454</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665913</v>
+        <v>665867</v>
       </c>
       <c r="R18" t="n">
-        <v>7185574</v>
+        <v>7185544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880439</v>
+        <v>119880424</v>
       </c>
       <c r="B26" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665731</v>
+        <v>665577</v>
       </c>
       <c r="R26" t="n">
-        <v>7185521</v>
+        <v>7185596</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880473</v>
+        <v>119880439</v>
       </c>
       <c r="B27" t="n">
-        <v>91852</v>
+        <v>89633</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3246,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>666000</v>
+        <v>665731</v>
       </c>
       <c r="R27" t="n">
-        <v>7185668</v>
+        <v>7185521</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880424</v>
+        <v>119880473</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665577</v>
+        <v>666000</v>
       </c>
       <c r="R28" t="n">
-        <v>7185596</v>
+        <v>7185668</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880433</v>
+        <v>119880471</v>
       </c>
       <c r="B36" t="n">
-        <v>91834</v>
+        <v>91828</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,25 +4179,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665516</v>
+        <v>665988</v>
       </c>
       <c r="R36" t="n">
-        <v>7185504</v>
+        <v>7185667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880471</v>
+        <v>119880446</v>
       </c>
       <c r="B37" t="n">
-        <v>91828</v>
+        <v>78171</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665988</v>
+        <v>665779</v>
       </c>
       <c r="R37" t="n">
-        <v>7185667</v>
+        <v>7185598</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880446</v>
+        <v>119880433</v>
       </c>
       <c r="B38" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665779</v>
+        <v>665516</v>
       </c>
       <c r="R38" t="n">
-        <v>7185598</v>
+        <v>7185504</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880409</v>
+        <v>119880418</v>
       </c>
       <c r="B40" t="n">
-        <v>89230</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,25 +4587,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1596</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665652</v>
+        <v>665618</v>
       </c>
       <c r="R40" t="n">
-        <v>7185701</v>
+        <v>7185647</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880418</v>
+        <v>119880409</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>89230</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,25 +4689,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>1596</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665618</v>
+        <v>665652</v>
       </c>
       <c r="R41" t="n">
-        <v>7185647</v>
+        <v>7185701</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880441</v>
+        <v>119880463</v>
       </c>
       <c r="B52" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665740</v>
+        <v>665918</v>
       </c>
       <c r="R52" t="n">
-        <v>7185522</v>
+        <v>7185620</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880443</v>
+        <v>119880441</v>
       </c>
       <c r="B53" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665746</v>
+        <v>665740</v>
       </c>
       <c r="R53" t="n">
-        <v>7185579</v>
+        <v>7185522</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880463</v>
+        <v>119880443</v>
       </c>
       <c r="B54" t="n">
-        <v>91826</v>
+        <v>91852</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665918</v>
+        <v>665746</v>
       </c>
       <c r="R54" t="n">
-        <v>7185620</v>
+        <v>7185579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880458</v>
+        <v>119880457</v>
       </c>
       <c r="B12" t="n">
-        <v>89252</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665911</v>
+        <v>665871</v>
       </c>
       <c r="R12" t="n">
-        <v>7185565</v>
+        <v>7185570</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880457</v>
+        <v>119880464</v>
       </c>
       <c r="B13" t="n">
         <v>91852</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665871</v>
+        <v>665922</v>
       </c>
       <c r="R13" t="n">
-        <v>7185570</v>
+        <v>7185624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880464</v>
+        <v>119880458</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>89252</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665922</v>
+        <v>665911</v>
       </c>
       <c r="R14" t="n">
-        <v>7185624</v>
+        <v>7185565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880398</v>
+        <v>119880430</v>
       </c>
       <c r="B22" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665837</v>
+        <v>665527</v>
       </c>
       <c r="R22" t="n">
-        <v>7185742</v>
+        <v>7185533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880413</v>
+        <v>119880398</v>
       </c>
       <c r="B23" t="n">
         <v>89275</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665629</v>
+        <v>665837</v>
       </c>
       <c r="R23" t="n">
-        <v>7185671</v>
+        <v>7185742</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880430</v>
+        <v>119880413</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,25 +2940,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665527</v>
+        <v>665629</v>
       </c>
       <c r="R24" t="n">
-        <v>7185533</v>
+        <v>7185671</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880424</v>
+        <v>119880439</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665577</v>
+        <v>665731</v>
       </c>
       <c r="R26" t="n">
-        <v>7185596</v>
+        <v>7185521</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880439</v>
+        <v>119880473</v>
       </c>
       <c r="B27" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3246,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665731</v>
+        <v>666000</v>
       </c>
       <c r="R27" t="n">
-        <v>7185521</v>
+        <v>7185668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880473</v>
+        <v>119880424</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>666000</v>
+        <v>665577</v>
       </c>
       <c r="R28" t="n">
-        <v>7185668</v>
+        <v>7185596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880418</v>
+        <v>119880409</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>89230</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,25 +4587,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>1596</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665618</v>
+        <v>665652</v>
       </c>
       <c r="R40" t="n">
-        <v>7185647</v>
+        <v>7185701</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880409</v>
+        <v>119880418</v>
       </c>
       <c r="B41" t="n">
-        <v>89230</v>
+        <v>91852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,25 +4689,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1596</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665652</v>
+        <v>665618</v>
       </c>
       <c r="R41" t="n">
-        <v>7185701</v>
+        <v>7185647</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880417</v>
+        <v>119880447</v>
       </c>
       <c r="B56" t="n">
-        <v>77458</v>
+        <v>91856</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6487</v>
+        <v>2059</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665632</v>
+        <v>665779</v>
       </c>
       <c r="R56" t="n">
-        <v>7185649</v>
+        <v>7185591</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880447</v>
+        <v>119880417</v>
       </c>
       <c r="B57" t="n">
-        <v>91856</v>
+        <v>77458</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>6487</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665779</v>
+        <v>665632</v>
       </c>
       <c r="R57" t="n">
-        <v>7185591</v>
+        <v>7185649</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880439</v>
+        <v>119880424</v>
       </c>
       <c r="B26" t="n">
-        <v>89633</v>
+        <v>91834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665731</v>
+        <v>665577</v>
       </c>
       <c r="R26" t="n">
-        <v>7185521</v>
+        <v>7185596</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880473</v>
+        <v>119880439</v>
       </c>
       <c r="B27" t="n">
-        <v>91852</v>
+        <v>89633</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3246,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>666000</v>
+        <v>665731</v>
       </c>
       <c r="R27" t="n">
-        <v>7185668</v>
+        <v>7185521</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880424</v>
+        <v>119880473</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665577</v>
+        <v>666000</v>
       </c>
       <c r="R28" t="n">
-        <v>7185596</v>
+        <v>7185668</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880409</v>
+        <v>119880418</v>
       </c>
       <c r="B40" t="n">
-        <v>89230</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,25 +4587,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1596</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665652</v>
+        <v>665618</v>
       </c>
       <c r="R40" t="n">
-        <v>7185701</v>
+        <v>7185647</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880418</v>
+        <v>119880409</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>89230</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,25 +4689,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>1596</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665618</v>
+        <v>665652</v>
       </c>
       <c r="R41" t="n">
-        <v>7185647</v>
+        <v>7185701</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880463</v>
+        <v>119880441</v>
       </c>
       <c r="B52" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665918</v>
+        <v>665740</v>
       </c>
       <c r="R52" t="n">
-        <v>7185620</v>
+        <v>7185522</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880441</v>
+        <v>119880443</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665740</v>
+        <v>665746</v>
       </c>
       <c r="R53" t="n">
-        <v>7185522</v>
+        <v>7185579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880443</v>
+        <v>119880463</v>
       </c>
       <c r="B54" t="n">
-        <v>91852</v>
+        <v>91826</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665746</v>
+        <v>665918</v>
       </c>
       <c r="R54" t="n">
-        <v>7185579</v>
+        <v>7185620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880456</v>
+        <v>119880454</v>
       </c>
       <c r="B15" t="n">
-        <v>78171</v>
+        <v>91832</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665872</v>
+        <v>665867</v>
       </c>
       <c r="R15" t="n">
-        <v>7185563</v>
+        <v>7185544</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880459</v>
+        <v>119880467</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665913</v>
+        <v>665967</v>
       </c>
       <c r="R16" t="n">
-        <v>7185574</v>
+        <v>7185660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880467</v>
+        <v>119880456</v>
       </c>
       <c r="B17" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665967</v>
+        <v>665872</v>
       </c>
       <c r="R17" t="n">
-        <v>7185660</v>
+        <v>7185563</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880454</v>
+        <v>119880459</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>78171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665867</v>
+        <v>665913</v>
       </c>
       <c r="R18" t="n">
-        <v>7185544</v>
+        <v>7185574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880424</v>
+        <v>119880439</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>89633</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665577</v>
+        <v>665731</v>
       </c>
       <c r="R26" t="n">
-        <v>7185596</v>
+        <v>7185521</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880439</v>
+        <v>119880473</v>
       </c>
       <c r="B27" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3246,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665731</v>
+        <v>666000</v>
       </c>
       <c r="R27" t="n">
-        <v>7185521</v>
+        <v>7185668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880473</v>
+        <v>119880424</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>666000</v>
+        <v>665577</v>
       </c>
       <c r="R28" t="n">
-        <v>7185668</v>
+        <v>7185596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880418</v>
+        <v>119880409</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>89230</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,25 +4587,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4366</v>
+        <v>1596</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665618</v>
+        <v>665652</v>
       </c>
       <c r="R40" t="n">
-        <v>7185647</v>
+        <v>7185701</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880409</v>
+        <v>119880418</v>
       </c>
       <c r="B41" t="n">
-        <v>89230</v>
+        <v>91852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,25 +4689,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1596</v>
+        <v>4366</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665652</v>
+        <v>665618</v>
       </c>
       <c r="R41" t="n">
-        <v>7185701</v>
+        <v>7185647</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880441</v>
+        <v>119880463</v>
       </c>
       <c r="B52" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665740</v>
+        <v>665918</v>
       </c>
       <c r="R52" t="n">
-        <v>7185522</v>
+        <v>7185620</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880443</v>
+        <v>119880441</v>
       </c>
       <c r="B53" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665746</v>
+        <v>665740</v>
       </c>
       <c r="R53" t="n">
-        <v>7185579</v>
+        <v>7185522</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880463</v>
+        <v>119880443</v>
       </c>
       <c r="B54" t="n">
-        <v>91826</v>
+        <v>91852</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665918</v>
+        <v>665746</v>
       </c>
       <c r="R54" t="n">
-        <v>7185620</v>
+        <v>7185579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880410</v>
+        <v>119880453</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91844</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665646</v>
+        <v>665867</v>
       </c>
       <c r="R3" t="n">
-        <v>7185686</v>
+        <v>7185548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880465</v>
+        <v>119880472</v>
       </c>
       <c r="B4" t="n">
-        <v>91828</v>
+        <v>91844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665944</v>
+        <v>665998</v>
       </c>
       <c r="R4" t="n">
-        <v>7185632</v>
+        <v>7185666</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
         <v>119880412</v>
       </c>
       <c r="B5" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880468</v>
+        <v>119880442</v>
       </c>
       <c r="B6" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665975</v>
+        <v>665744</v>
       </c>
       <c r="R6" t="n">
-        <v>7185666</v>
+        <v>7185572</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880431</v>
+        <v>119880433</v>
       </c>
       <c r="B7" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665509</v>
+        <v>665516</v>
       </c>
       <c r="R7" t="n">
-        <v>7185520</v>
+        <v>7185504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880461</v>
+        <v>119880466</v>
       </c>
       <c r="B8" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665905</v>
+        <v>665966</v>
       </c>
       <c r="R8" t="n">
-        <v>7185598</v>
+        <v>7185634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880438</v>
+        <v>119880455</v>
       </c>
       <c r="B9" t="n">
-        <v>91844</v>
+        <v>89292</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665723</v>
+        <v>665872</v>
       </c>
       <c r="R9" t="n">
-        <v>7185514</v>
+        <v>7185555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880423</v>
+        <v>119880444</v>
       </c>
       <c r="B10" t="n">
-        <v>78263</v>
+        <v>89650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665584</v>
+        <v>665746</v>
       </c>
       <c r="R10" t="n">
-        <v>7185605</v>
+        <v>7185579</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880440</v>
+        <v>119880465</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
+        <v>91846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665733</v>
+        <v>665944</v>
       </c>
       <c r="R11" t="n">
-        <v>7185520</v>
+        <v>7185632</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880457</v>
+        <v>119880418</v>
       </c>
       <c r="B12" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665871</v>
+        <v>665618</v>
       </c>
       <c r="R12" t="n">
-        <v>7185570</v>
+        <v>7185647</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1806,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880464</v>
+        <v>119880424</v>
       </c>
       <c r="B13" t="n">
         <v>91852</v>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665922</v>
+        <v>665577</v>
       </c>
       <c r="R13" t="n">
-        <v>7185624</v>
+        <v>7185596</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880458</v>
+        <v>119880447</v>
       </c>
       <c r="B14" t="n">
-        <v>89252</v>
+        <v>91874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665911</v>
+        <v>665779</v>
       </c>
       <c r="R14" t="n">
-        <v>7185565</v>
+        <v>7185591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880454</v>
+        <v>119880468</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665867</v>
+        <v>665975</v>
       </c>
       <c r="R15" t="n">
-        <v>7185544</v>
+        <v>7185666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880467</v>
+        <v>119880448</v>
       </c>
       <c r="B16" t="n">
-        <v>89252</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665967</v>
+        <v>665801</v>
       </c>
       <c r="R16" t="n">
-        <v>7185660</v>
+        <v>7185555</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880456</v>
+        <v>119880431</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
+        <v>78187</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665872</v>
+        <v>665509</v>
       </c>
       <c r="R17" t="n">
-        <v>7185563</v>
+        <v>7185520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880459</v>
+        <v>119880438</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
+        <v>91862</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2328,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665913</v>
+        <v>665723</v>
       </c>
       <c r="R18" t="n">
-        <v>7185574</v>
+        <v>7185514</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880425</v>
+        <v>119880450</v>
       </c>
       <c r="B19" t="n">
-        <v>89633</v>
+        <v>89650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665574</v>
+        <v>665811</v>
       </c>
       <c r="R19" t="n">
-        <v>7185592</v>
+        <v>7185566</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880444</v>
+        <v>119880456</v>
       </c>
       <c r="B20" t="n">
-        <v>89633</v>
+        <v>78187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665746</v>
+        <v>665872</v>
       </c>
       <c r="R20" t="n">
-        <v>7185579</v>
+        <v>7185563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880411</v>
+        <v>119880449</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665645</v>
+        <v>665811</v>
       </c>
       <c r="R21" t="n">
-        <v>7185685</v>
+        <v>7185566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880430</v>
+        <v>119880470</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>89269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665527</v>
+        <v>665982</v>
       </c>
       <c r="R22" t="n">
-        <v>7185533</v>
+        <v>7185672</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880398</v>
+        <v>119880410</v>
       </c>
       <c r="B23" t="n">
-        <v>89275</v>
+        <v>91850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,25 +2838,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665837</v>
+        <v>665646</v>
       </c>
       <c r="R23" t="n">
-        <v>7185742</v>
+        <v>7185686</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880413</v>
+        <v>119880398</v>
       </c>
       <c r="B24" t="n">
-        <v>89275</v>
+        <v>89292</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665629</v>
+        <v>665837</v>
       </c>
       <c r="R24" t="n">
-        <v>7185671</v>
+        <v>7185742</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880455</v>
+        <v>119880427</v>
       </c>
       <c r="B25" t="n">
-        <v>89275</v>
+        <v>78187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665872</v>
+        <v>665573</v>
       </c>
       <c r="R25" t="n">
-        <v>7185555</v>
+        <v>7185584</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880439</v>
+        <v>119880428</v>
       </c>
       <c r="B26" t="n">
-        <v>89633</v>
+        <v>91902</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665731</v>
+        <v>665530</v>
       </c>
       <c r="R26" t="n">
-        <v>7185521</v>
+        <v>7185543</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880473</v>
+        <v>119880425</v>
       </c>
       <c r="B27" t="n">
-        <v>91852</v>
+        <v>89650</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3246,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>666000</v>
+        <v>665574</v>
       </c>
       <c r="R27" t="n">
-        <v>7185668</v>
+        <v>7185592</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880424</v>
+        <v>119880462</v>
       </c>
       <c r="B28" t="n">
-        <v>91834</v>
+        <v>89269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665577</v>
+        <v>665918</v>
       </c>
       <c r="R28" t="n">
-        <v>7185596</v>
+        <v>7185620</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880451</v>
+        <v>119880473</v>
       </c>
       <c r="B29" t="n">
-        <v>78171</v>
+        <v>91870</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,25 +3450,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665824</v>
+        <v>666000</v>
       </c>
       <c r="R29" t="n">
-        <v>7185574</v>
+        <v>7185668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880437</v>
+        <v>119880445</v>
       </c>
       <c r="B30" t="n">
-        <v>79643</v>
+        <v>78187</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,25 +3552,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665631</v>
+        <v>665752</v>
       </c>
       <c r="R30" t="n">
-        <v>7185482</v>
+        <v>7185584</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,21 +3626,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3657,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880453</v>
+        <v>119880457</v>
       </c>
       <c r="B31" t="n">
-        <v>91826</v>
+        <v>91870</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,25 +3654,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665867</v>
+        <v>665871</v>
       </c>
       <c r="R31" t="n">
-        <v>7185548</v>
+        <v>7185570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880442</v>
+        <v>119880443</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91870</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3771,25 +3756,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665744</v>
+        <v>665746</v>
       </c>
       <c r="R32" t="n">
-        <v>7185572</v>
+        <v>7185579</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3861,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880452</v>
+        <v>119880464</v>
       </c>
       <c r="B33" t="n">
-        <v>91826</v>
+        <v>91870</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3873,25 +3858,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665842</v>
+        <v>665922</v>
       </c>
       <c r="R33" t="n">
-        <v>7185565</v>
+        <v>7185624</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880429</v>
+        <v>119880459</v>
       </c>
       <c r="B34" t="n">
-        <v>91883</v>
+        <v>78187</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3979,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665527</v>
+        <v>665913</v>
       </c>
       <c r="R34" t="n">
-        <v>7185533</v>
+        <v>7185574</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,10 +4050,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880448</v>
+        <v>119880440</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4081,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4105,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665801</v>
+        <v>665733</v>
       </c>
       <c r="R35" t="n">
-        <v>7185555</v>
+        <v>7185520</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,10 +4152,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880471</v>
+        <v>119880409</v>
       </c>
       <c r="B36" t="n">
-        <v>91828</v>
+        <v>89247</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>1596</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665988</v>
+        <v>665652</v>
       </c>
       <c r="R36" t="n">
-        <v>7185667</v>
+        <v>7185701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4254,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880446</v>
+        <v>119880429</v>
       </c>
       <c r="B37" t="n">
-        <v>78171</v>
+        <v>91901</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,21 +4270,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4294,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665779</v>
+        <v>665527</v>
       </c>
       <c r="R37" t="n">
-        <v>7185598</v>
+        <v>7185533</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,10 +4356,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880433</v>
+        <v>119880414</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>78187</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,21 +4372,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4396,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665516</v>
+        <v>665625</v>
       </c>
       <c r="R38" t="n">
-        <v>7185504</v>
+        <v>7185661</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,10 +4458,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880445</v>
+        <v>119880441</v>
       </c>
       <c r="B39" t="n">
-        <v>78171</v>
+        <v>91852</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4489,21 +4474,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4513,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665752</v>
+        <v>665740</v>
       </c>
       <c r="R39" t="n">
-        <v>7185584</v>
+        <v>7185522</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4575,10 +4560,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880409</v>
+        <v>119880446</v>
       </c>
       <c r="B40" t="n">
-        <v>89230</v>
+        <v>78187</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4587,25 +4572,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1596</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665652</v>
+        <v>665779</v>
       </c>
       <c r="R40" t="n">
-        <v>7185701</v>
+        <v>7185598</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4662,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880418</v>
+        <v>119880467</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4689,25 +4674,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4702,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665618</v>
+        <v>665967</v>
       </c>
       <c r="R41" t="n">
-        <v>7185647</v>
+        <v>7185660</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4779,10 +4764,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880472</v>
+        <v>119880458</v>
       </c>
       <c r="B42" t="n">
-        <v>91826</v>
+        <v>89269</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,25 +4776,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4804,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665998</v>
+        <v>665911</v>
       </c>
       <c r="R42" t="n">
-        <v>7185666</v>
+        <v>7185565</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4866,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880419</v>
+        <v>119880439</v>
       </c>
       <c r="B43" t="n">
-        <v>78171</v>
+        <v>89650</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,21 +4882,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665600</v>
+        <v>665731</v>
       </c>
       <c r="R43" t="n">
-        <v>7185629</v>
+        <v>7185521</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4968,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880470</v>
+        <v>119880460</v>
       </c>
       <c r="B44" t="n">
-        <v>89252</v>
+        <v>91850</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +4980,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5008,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665982</v>
+        <v>665910</v>
       </c>
       <c r="R44" t="n">
-        <v>7185672</v>
+        <v>7185584</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5070,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880428</v>
+        <v>119880463</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>91844</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,21 +5086,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5110,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665530</v>
+        <v>665918</v>
       </c>
       <c r="R45" t="n">
-        <v>7185543</v>
+        <v>7185620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,10 +5172,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880462</v>
+        <v>119880419</v>
       </c>
       <c r="B46" t="n">
-        <v>89252</v>
+        <v>78187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,25 +5184,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665918</v>
+        <v>665600</v>
       </c>
       <c r="R46" t="n">
-        <v>7185620</v>
+        <v>7185629</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880449</v>
+        <v>119880413</v>
       </c>
       <c r="B47" t="n">
-        <v>78171</v>
+        <v>89292</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,25 +5286,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5314,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665811</v>
+        <v>665629</v>
       </c>
       <c r="R47" t="n">
-        <v>7185566</v>
+        <v>7185671</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,10 +5376,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880427</v>
+        <v>119880454</v>
       </c>
       <c r="B48" t="n">
-        <v>78171</v>
+        <v>91850</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,21 +5392,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5416,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665573</v>
+        <v>665867</v>
       </c>
       <c r="R48" t="n">
-        <v>7185584</v>
+        <v>7185544</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880414</v>
+        <v>119880471</v>
       </c>
       <c r="B49" t="n">
-        <v>78171</v>
+        <v>91846</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,25 +5490,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665625</v>
+        <v>665988</v>
       </c>
       <c r="R49" t="n">
-        <v>7185661</v>
+        <v>7185667</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5580,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880466</v>
+        <v>119880437</v>
       </c>
       <c r="B50" t="n">
-        <v>91832</v>
+        <v>79659</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,25 +5592,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5620,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665966</v>
+        <v>665631</v>
       </c>
       <c r="R50" t="n">
-        <v>7185634</v>
+        <v>7185482</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5681,6 +5666,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880450</v>
+        <v>119880451</v>
       </c>
       <c r="B51" t="n">
-        <v>89633</v>
+        <v>78187</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665811</v>
+        <v>665824</v>
       </c>
       <c r="R51" t="n">
-        <v>7185566</v>
+        <v>7185574</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880463</v>
+        <v>119880452</v>
       </c>
       <c r="B52" t="n">
-        <v>91826</v>
+        <v>91844</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665918</v>
+        <v>665842</v>
       </c>
       <c r="R52" t="n">
-        <v>7185620</v>
+        <v>7185565</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880441</v>
+        <v>119880461</v>
       </c>
       <c r="B53" t="n">
-        <v>91834</v>
+        <v>91862</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665740</v>
+        <v>665905</v>
       </c>
       <c r="R53" t="n">
-        <v>7185522</v>
+        <v>7185598</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880443</v>
+        <v>119880411</v>
       </c>
       <c r="B54" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6019,21 +6019,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665746</v>
+        <v>665645</v>
       </c>
       <c r="R54" t="n">
-        <v>7185579</v>
+        <v>7185685</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880460</v>
+        <v>119880417</v>
       </c>
       <c r="B55" t="n">
-        <v>91832</v>
+        <v>77474</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6121,21 +6121,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>6487</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665910</v>
+        <v>665632</v>
       </c>
       <c r="R55" t="n">
-        <v>7185584</v>
+        <v>7185649</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880447</v>
+        <v>119880430</v>
       </c>
       <c r="B56" t="n">
-        <v>91856</v>
+        <v>91850</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665779</v>
+        <v>665527</v>
       </c>
       <c r="R56" t="n">
-        <v>7185591</v>
+        <v>7185533</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880417</v>
+        <v>119880423</v>
       </c>
       <c r="B57" t="n">
-        <v>77458</v>
+        <v>78279</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665632</v>
+        <v>665584</v>
       </c>
       <c r="R57" t="n">
-        <v>7185649</v>
+        <v>7185605</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880447</v>
+        <v>119880468</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665779</v>
+        <v>665975</v>
       </c>
       <c r="R14" t="n">
-        <v>7185591</v>
+        <v>7185666</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880468</v>
+        <v>119880448</v>
       </c>
       <c r="B15" t="n">
-        <v>79160</v>
+        <v>91852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665975</v>
+        <v>665801</v>
       </c>
       <c r="R15" t="n">
-        <v>7185666</v>
+        <v>7185555</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880448</v>
+        <v>119880447</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665801</v>
+        <v>665779</v>
       </c>
       <c r="R16" t="n">
-        <v>7185555</v>
+        <v>7185591</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880462</v>
+        <v>119880445</v>
       </c>
       <c r="B28" t="n">
-        <v>89269</v>
+        <v>78187</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665918</v>
+        <v>665752</v>
       </c>
       <c r="R28" t="n">
-        <v>7185620</v>
+        <v>7185584</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880473</v>
+        <v>119880462</v>
       </c>
       <c r="B29" t="n">
-        <v>91870</v>
+        <v>89269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,25 +3450,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>666000</v>
+        <v>665918</v>
       </c>
       <c r="R29" t="n">
-        <v>7185668</v>
+        <v>7185620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880445</v>
+        <v>119880473</v>
       </c>
       <c r="B30" t="n">
-        <v>78187</v>
+        <v>91870</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,25 +3552,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665752</v>
+        <v>666000</v>
       </c>
       <c r="R30" t="n">
-        <v>7185584</v>
+        <v>7185668</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5274,10 +5274,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880413</v>
+        <v>119880471</v>
       </c>
       <c r="B47" t="n">
-        <v>89292</v>
+        <v>91846</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5290,21 +5290,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6286</v>
+        <v>149</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665629</v>
+        <v>665988</v>
       </c>
       <c r="R47" t="n">
-        <v>7185671</v>
+        <v>7185667</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880454</v>
+        <v>119880413</v>
       </c>
       <c r="B48" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5388,25 +5388,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665867</v>
+        <v>665629</v>
       </c>
       <c r="R48" t="n">
-        <v>7185544</v>
+        <v>7185671</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880471</v>
+        <v>119880454</v>
       </c>
       <c r="B49" t="n">
-        <v>91846</v>
+        <v>91850</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5490,25 +5490,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665988</v>
+        <v>665867</v>
       </c>
       <c r="R49" t="n">
-        <v>7185667</v>
+        <v>7185544</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880451</v>
+        <v>119880452</v>
       </c>
       <c r="B51" t="n">
-        <v>78187</v>
+        <v>91844</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665824</v>
+        <v>665842</v>
       </c>
       <c r="R51" t="n">
-        <v>7185574</v>
+        <v>7185565</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880452</v>
+        <v>119880451</v>
       </c>
       <c r="B52" t="n">
-        <v>91844</v>
+        <v>78187</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665842</v>
+        <v>665824</v>
       </c>
       <c r="R52" t="n">
-        <v>7185565</v>
+        <v>7185574</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880453</v>
+        <v>119880451</v>
       </c>
       <c r="B3" t="n">
-        <v>91844</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665867</v>
+        <v>665824</v>
       </c>
       <c r="R3" t="n">
-        <v>7185548</v>
+        <v>7185574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880472</v>
+        <v>119880413</v>
       </c>
       <c r="B4" t="n">
-        <v>91844</v>
+        <v>89292</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3100</v>
+        <v>6286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665998</v>
+        <v>665629</v>
       </c>
       <c r="R4" t="n">
-        <v>7185666</v>
+        <v>7185671</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880412</v>
+        <v>119880410</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665642</v>
+        <v>665646</v>
       </c>
       <c r="R5" t="n">
-        <v>7185682</v>
+        <v>7185686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880442</v>
+        <v>119880419</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665744</v>
+        <v>665600</v>
       </c>
       <c r="R6" t="n">
-        <v>7185572</v>
+        <v>7185629</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880433</v>
+        <v>119880418</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665516</v>
+        <v>665618</v>
       </c>
       <c r="R7" t="n">
-        <v>7185504</v>
+        <v>7185647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880466</v>
+        <v>119880424</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665966</v>
+        <v>665577</v>
       </c>
       <c r="R8" t="n">
-        <v>7185634</v>
+        <v>7185596</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880455</v>
+        <v>119880398</v>
       </c>
       <c r="B9" t="n">
         <v>89292</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665872</v>
+        <v>665837</v>
       </c>
       <c r="R9" t="n">
-        <v>7185555</v>
+        <v>7185742</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880444</v>
+        <v>119880458</v>
       </c>
       <c r="B10" t="n">
-        <v>89650</v>
+        <v>89269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665746</v>
+        <v>665911</v>
       </c>
       <c r="R10" t="n">
-        <v>7185579</v>
+        <v>7185565</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880465</v>
+        <v>119880453</v>
       </c>
       <c r="B11" t="n">
-        <v>91846</v>
+        <v>91844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665944</v>
+        <v>665867</v>
       </c>
       <c r="R11" t="n">
-        <v>7185632</v>
+        <v>7185548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880418</v>
+        <v>119880463</v>
       </c>
       <c r="B12" t="n">
-        <v>91870</v>
+        <v>91844</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665618</v>
+        <v>665918</v>
       </c>
       <c r="R12" t="n">
-        <v>7185647</v>
+        <v>7185620</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880424</v>
+        <v>119880461</v>
       </c>
       <c r="B13" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665577</v>
+        <v>665905</v>
       </c>
       <c r="R13" t="n">
-        <v>7185596</v>
+        <v>7185598</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880468</v>
+        <v>119880470</v>
       </c>
       <c r="B14" t="n">
-        <v>79160</v>
+        <v>89269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665975</v>
+        <v>665982</v>
       </c>
       <c r="R14" t="n">
-        <v>7185666</v>
+        <v>7185672</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880448</v>
+        <v>119880449</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665801</v>
+        <v>665811</v>
       </c>
       <c r="R15" t="n">
-        <v>7185555</v>
+        <v>7185566</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880447</v>
+        <v>119880409</v>
       </c>
       <c r="B16" t="n">
-        <v>91874</v>
+        <v>89247</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>1596</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665779</v>
+        <v>665652</v>
       </c>
       <c r="R16" t="n">
-        <v>7185591</v>
+        <v>7185701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880431</v>
+        <v>119880437</v>
       </c>
       <c r="B17" t="n">
-        <v>78187</v>
+        <v>79659</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665509</v>
+        <v>665631</v>
       </c>
       <c r="R17" t="n">
-        <v>7185520</v>
+        <v>7185482</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,6 +2300,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2316,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880438</v>
+        <v>119880467</v>
       </c>
       <c r="B18" t="n">
-        <v>91862</v>
+        <v>89269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2347,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665723</v>
+        <v>665967</v>
       </c>
       <c r="R18" t="n">
-        <v>7185514</v>
+        <v>7185660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880450</v>
+        <v>119880417</v>
       </c>
       <c r="B19" t="n">
-        <v>89650</v>
+        <v>77474</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665811</v>
+        <v>665632</v>
       </c>
       <c r="R19" t="n">
-        <v>7185566</v>
+        <v>7185649</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880456</v>
+        <v>119880448</v>
       </c>
       <c r="B20" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2551,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665872</v>
+        <v>665801</v>
       </c>
       <c r="R20" t="n">
-        <v>7185563</v>
+        <v>7185555</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880449</v>
+        <v>119880423</v>
       </c>
       <c r="B21" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2653,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2677,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665811</v>
+        <v>665584</v>
       </c>
       <c r="R21" t="n">
-        <v>7185566</v>
+        <v>7185605</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880470</v>
+        <v>119880465</v>
       </c>
       <c r="B22" t="n">
-        <v>89269</v>
+        <v>91846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2755,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665982</v>
+        <v>665944</v>
       </c>
       <c r="R22" t="n">
-        <v>7185672</v>
+        <v>7185632</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880410</v>
+        <v>119880457</v>
       </c>
       <c r="B23" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,25 +2853,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665646</v>
+        <v>665871</v>
       </c>
       <c r="R23" t="n">
-        <v>7185686</v>
+        <v>7185570</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880398</v>
+        <v>119880466</v>
       </c>
       <c r="B24" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,25 +2955,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665837</v>
+        <v>665966</v>
       </c>
       <c r="R24" t="n">
-        <v>7185742</v>
+        <v>7185634</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880427</v>
+        <v>119880460</v>
       </c>
       <c r="B25" t="n">
-        <v>78187</v>
+        <v>91850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3046,21 +3061,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,7 +3085,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665573</v>
+        <v>665910</v>
       </c>
       <c r="R25" t="n">
         <v>7185584</v>
@@ -3132,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880428</v>
+        <v>119880455</v>
       </c>
       <c r="B26" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3159,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665530</v>
+        <v>665872</v>
       </c>
       <c r="R26" t="n">
-        <v>7185543</v>
+        <v>7185555</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880425</v>
+        <v>119880456</v>
       </c>
       <c r="B27" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3250,21 +3265,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665574</v>
+        <v>665872</v>
       </c>
       <c r="R27" t="n">
-        <v>7185592</v>
+        <v>7185563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,10 +3351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880445</v>
+        <v>119880468</v>
       </c>
       <c r="B28" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665752</v>
+        <v>665975</v>
       </c>
       <c r="R28" t="n">
-        <v>7185584</v>
+        <v>7185666</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880473</v>
+        <v>119880438</v>
       </c>
       <c r="B30" t="n">
-        <v>91870</v>
+        <v>91862</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3552,25 +3567,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3595,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>666000</v>
+        <v>665723</v>
       </c>
       <c r="R30" t="n">
-        <v>7185668</v>
+        <v>7185514</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880457</v>
+        <v>119880445</v>
       </c>
       <c r="B31" t="n">
-        <v>91870</v>
+        <v>78187</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3654,25 +3669,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665871</v>
+        <v>665752</v>
       </c>
       <c r="R31" t="n">
-        <v>7185570</v>
+        <v>7185584</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880443</v>
+        <v>119880446</v>
       </c>
       <c r="B32" t="n">
-        <v>91870</v>
+        <v>78187</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3756,25 +3771,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3784,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665746</v>
+        <v>665779</v>
       </c>
       <c r="R32" t="n">
-        <v>7185579</v>
+        <v>7185598</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880464</v>
+        <v>119880444</v>
       </c>
       <c r="B33" t="n">
-        <v>91870</v>
+        <v>89650</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3858,25 +3873,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665922</v>
+        <v>665746</v>
       </c>
       <c r="R33" t="n">
-        <v>7185624</v>
+        <v>7185579</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3948,7 +3963,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880459</v>
+        <v>119880414</v>
       </c>
       <c r="B34" t="n">
         <v>78187</v>
@@ -3988,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665913</v>
+        <v>665625</v>
       </c>
       <c r="R34" t="n">
-        <v>7185574</v>
+        <v>7185661</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4050,10 +4065,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880440</v>
+        <v>119880464</v>
       </c>
       <c r="B35" t="n">
-        <v>78187</v>
+        <v>91870</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4062,25 +4077,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665733</v>
+        <v>665922</v>
       </c>
       <c r="R35" t="n">
-        <v>7185520</v>
+        <v>7185624</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4152,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880409</v>
+        <v>119880471</v>
       </c>
       <c r="B36" t="n">
-        <v>89247</v>
+        <v>91846</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4168,21 +4183,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1596</v>
+        <v>149</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665652</v>
+        <v>665988</v>
       </c>
       <c r="R36" t="n">
-        <v>7185701</v>
+        <v>7185667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880414</v>
+        <v>119880433</v>
       </c>
       <c r="B38" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4372,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4396,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665625</v>
+        <v>665516</v>
       </c>
       <c r="R38" t="n">
-        <v>7185661</v>
+        <v>7185504</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880441</v>
+        <v>119880430</v>
       </c>
       <c r="B39" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4474,21 +4489,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4498,10 +4513,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665740</v>
+        <v>665527</v>
       </c>
       <c r="R39" t="n">
-        <v>7185522</v>
+        <v>7185533</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,7 +4575,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880446</v>
+        <v>119880412</v>
       </c>
       <c r="B40" t="n">
         <v>78187</v>
@@ -4600,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665779</v>
+        <v>665642</v>
       </c>
       <c r="R40" t="n">
-        <v>7185598</v>
+        <v>7185682</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880467</v>
+        <v>119880431</v>
       </c>
       <c r="B41" t="n">
-        <v>89269</v>
+        <v>78187</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4674,25 +4689,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4702,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665967</v>
+        <v>665509</v>
       </c>
       <c r="R41" t="n">
-        <v>7185660</v>
+        <v>7185520</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4764,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880458</v>
+        <v>119880442</v>
       </c>
       <c r="B42" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4776,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4804,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665911</v>
+        <v>665744</v>
       </c>
       <c r="R42" t="n">
-        <v>7185565</v>
+        <v>7185572</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4866,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880439</v>
+        <v>119880440</v>
       </c>
       <c r="B43" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4882,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4906,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665731</v>
+        <v>665733</v>
       </c>
       <c r="R43" t="n">
-        <v>7185521</v>
+        <v>7185520</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880460</v>
+        <v>119880441</v>
       </c>
       <c r="B44" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4984,21 +4999,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5008,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665910</v>
+        <v>665740</v>
       </c>
       <c r="R44" t="n">
-        <v>7185584</v>
+        <v>7185522</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5070,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880463</v>
+        <v>119880443</v>
       </c>
       <c r="B45" t="n">
-        <v>91844</v>
+        <v>91870</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5082,25 +5097,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5110,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665918</v>
+        <v>665746</v>
       </c>
       <c r="R45" t="n">
-        <v>7185620</v>
+        <v>7185579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5172,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880419</v>
+        <v>119880425</v>
       </c>
       <c r="B46" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5188,21 +5203,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5212,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665600</v>
+        <v>665574</v>
       </c>
       <c r="R46" t="n">
-        <v>7185629</v>
+        <v>7185592</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5274,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880471</v>
+        <v>119880447</v>
       </c>
       <c r="B47" t="n">
-        <v>91846</v>
+        <v>91874</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5286,25 +5301,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>149</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5314,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665988</v>
+        <v>665779</v>
       </c>
       <c r="R47" t="n">
-        <v>7185667</v>
+        <v>7185591</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880413</v>
+        <v>119880450</v>
       </c>
       <c r="B48" t="n">
-        <v>89292</v>
+        <v>89650</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5388,25 +5403,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6286</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5416,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665629</v>
+        <v>665811</v>
       </c>
       <c r="R48" t="n">
-        <v>7185671</v>
+        <v>7185566</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880454</v>
+        <v>119880452</v>
       </c>
       <c r="B49" t="n">
-        <v>91850</v>
+        <v>91844</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5494,21 +5509,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665867</v>
+        <v>665842</v>
       </c>
       <c r="R49" t="n">
-        <v>7185544</v>
+        <v>7185565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5580,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880437</v>
+        <v>119880427</v>
       </c>
       <c r="B50" t="n">
-        <v>79659</v>
+        <v>78187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5592,25 +5607,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5620,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665631</v>
+        <v>665573</v>
       </c>
       <c r="R50" t="n">
-        <v>7185482</v>
+        <v>7185584</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5666,21 +5681,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880452</v>
+        <v>119880428</v>
       </c>
       <c r="B51" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665842</v>
+        <v>665530</v>
       </c>
       <c r="R51" t="n">
-        <v>7185565</v>
+        <v>7185543</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880451</v>
+        <v>119880411</v>
       </c>
       <c r="B52" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,25 +5811,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665824</v>
+        <v>665645</v>
       </c>
       <c r="R52" t="n">
-        <v>7185574</v>
+        <v>7185685</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880461</v>
+        <v>119880472</v>
       </c>
       <c r="B53" t="n">
-        <v>91862</v>
+        <v>91844</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665905</v>
+        <v>665998</v>
       </c>
       <c r="R53" t="n">
-        <v>7185598</v>
+        <v>7185666</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880411</v>
+        <v>119880459</v>
       </c>
       <c r="B54" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665645</v>
+        <v>665913</v>
       </c>
       <c r="R54" t="n">
-        <v>7185685</v>
+        <v>7185574</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880417</v>
+        <v>119880473</v>
       </c>
       <c r="B55" t="n">
-        <v>77474</v>
+        <v>91870</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6117,25 +6117,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6487</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665632</v>
+        <v>666000</v>
       </c>
       <c r="R55" t="n">
-        <v>7185649</v>
+        <v>7185668</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,7 +6207,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880430</v>
+        <v>119880454</v>
       </c>
       <c r="B56" t="n">
         <v>91850</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665527</v>
+        <v>665867</v>
       </c>
       <c r="R56" t="n">
-        <v>7185533</v>
+        <v>7185544</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880423</v>
+        <v>119880439</v>
       </c>
       <c r="B57" t="n">
-        <v>78279</v>
+        <v>89650</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665584</v>
+        <v>665731</v>
       </c>
       <c r="R57" t="n">
-        <v>7185605</v>
+        <v>7185521</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880449</v>
+        <v>119880437</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>79659</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665811</v>
+        <v>665631</v>
       </c>
       <c r="R15" t="n">
-        <v>7185566</v>
+        <v>7185482</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,6 +2096,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2112,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880409</v>
+        <v>119880467</v>
       </c>
       <c r="B16" t="n">
-        <v>89247</v>
+        <v>89269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2143,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1596</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665652</v>
+        <v>665967</v>
       </c>
       <c r="R16" t="n">
-        <v>7185701</v>
+        <v>7185660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880437</v>
+        <v>119880417</v>
       </c>
       <c r="B17" t="n">
-        <v>79659</v>
+        <v>77474</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2241,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665631</v>
+        <v>665632</v>
       </c>
       <c r="R17" t="n">
-        <v>7185482</v>
+        <v>7185649</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,21 +2315,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880467</v>
+        <v>119880423</v>
       </c>
       <c r="B18" t="n">
-        <v>89269</v>
+        <v>78279</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665967</v>
+        <v>665584</v>
       </c>
       <c r="R18" t="n">
-        <v>7185660</v>
+        <v>7185605</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880417</v>
+        <v>119880449</v>
       </c>
       <c r="B19" t="n">
-        <v>77474</v>
+        <v>78187</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665632</v>
+        <v>665811</v>
       </c>
       <c r="R19" t="n">
-        <v>7185649</v>
+        <v>7185566</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880448</v>
+        <v>119880409</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>89247</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,25 +2547,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665801</v>
+        <v>665652</v>
       </c>
       <c r="R20" t="n">
-        <v>7185555</v>
+        <v>7185701</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880423</v>
+        <v>119880448</v>
       </c>
       <c r="B21" t="n">
-        <v>78279</v>
+        <v>91852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665584</v>
+        <v>665801</v>
       </c>
       <c r="R21" t="n">
-        <v>7185605</v>
+        <v>7185555</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880465</v>
+        <v>119880457</v>
       </c>
       <c r="B22" t="n">
-        <v>91846</v>
+        <v>91870</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,25 +2751,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665944</v>
+        <v>665871</v>
       </c>
       <c r="R22" t="n">
-        <v>7185632</v>
+        <v>7185570</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880457</v>
+        <v>119880455</v>
       </c>
       <c r="B23" t="n">
-        <v>91870</v>
+        <v>89292</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,25 +2853,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665871</v>
+        <v>665872</v>
       </c>
       <c r="R23" t="n">
-        <v>7185570</v>
+        <v>7185555</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880466</v>
+        <v>119880460</v>
       </c>
       <c r="B24" t="n">
         <v>91850</v>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665966</v>
+        <v>665910</v>
       </c>
       <c r="R24" t="n">
-        <v>7185634</v>
+        <v>7185584</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880460</v>
+        <v>119880465</v>
       </c>
       <c r="B25" t="n">
-        <v>91850</v>
+        <v>91846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,25 +3057,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665910</v>
+        <v>665944</v>
       </c>
       <c r="R25" t="n">
-        <v>7185584</v>
+        <v>7185632</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880455</v>
+        <v>119880466</v>
       </c>
       <c r="B26" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,25 +3159,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665872</v>
+        <v>665966</v>
       </c>
       <c r="R26" t="n">
-        <v>7185555</v>
+        <v>7185634</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880452</v>
+        <v>119880427</v>
       </c>
       <c r="B49" t="n">
-        <v>91844</v>
+        <v>78187</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665842</v>
+        <v>665573</v>
       </c>
       <c r="R49" t="n">
-        <v>7185565</v>
+        <v>7185584</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880427</v>
+        <v>119880452</v>
       </c>
       <c r="B50" t="n">
-        <v>78187</v>
+        <v>91844</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,21 +5611,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665573</v>
+        <v>665842</v>
       </c>
       <c r="R50" t="n">
-        <v>7185584</v>
+        <v>7185565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880451</v>
+        <v>119880438</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
+        <v>91862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665824</v>
+        <v>665723</v>
       </c>
       <c r="R3" t="n">
-        <v>7185574</v>
+        <v>7185514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880413</v>
+        <v>119880411</v>
       </c>
       <c r="B4" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665629</v>
+        <v>665645</v>
       </c>
       <c r="R4" t="n">
-        <v>7185671</v>
+        <v>7185685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880410</v>
+        <v>119880457</v>
       </c>
       <c r="B5" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665646</v>
+        <v>665871</v>
       </c>
       <c r="R5" t="n">
-        <v>7185686</v>
+        <v>7185570</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880419</v>
+        <v>119880450</v>
       </c>
       <c r="B6" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665600</v>
+        <v>665811</v>
       </c>
       <c r="R6" t="n">
-        <v>7185629</v>
+        <v>7185566</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880418</v>
+        <v>119880428</v>
       </c>
       <c r="B7" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665618</v>
+        <v>665530</v>
       </c>
       <c r="R7" t="n">
-        <v>7185647</v>
+        <v>7185543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880424</v>
+        <v>119880460</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665577</v>
+        <v>665910</v>
       </c>
       <c r="R8" t="n">
-        <v>7185596</v>
+        <v>7185584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880398</v>
+        <v>119880455</v>
       </c>
       <c r="B9" t="n">
         <v>89292</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665837</v>
+        <v>665872</v>
       </c>
       <c r="R9" t="n">
-        <v>7185742</v>
+        <v>7185555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880458</v>
+        <v>119880410</v>
       </c>
       <c r="B10" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665911</v>
+        <v>665646</v>
       </c>
       <c r="R10" t="n">
-        <v>7185565</v>
+        <v>7185686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880453</v>
+        <v>119880454</v>
       </c>
       <c r="B11" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1645,7 +1645,7 @@
         <v>665867</v>
       </c>
       <c r="R11" t="n">
-        <v>7185548</v>
+        <v>7185544</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880463</v>
+        <v>119880444</v>
       </c>
       <c r="B12" t="n">
-        <v>91844</v>
+        <v>89650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665918</v>
+        <v>665746</v>
       </c>
       <c r="R12" t="n">
-        <v>7185620</v>
+        <v>7185579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880461</v>
+        <v>119880472</v>
       </c>
       <c r="B13" t="n">
-        <v>91862</v>
+        <v>91844</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665905</v>
+        <v>665998</v>
       </c>
       <c r="R13" t="n">
-        <v>7185598</v>
+        <v>7185666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880437</v>
+        <v>119880448</v>
       </c>
       <c r="B15" t="n">
-        <v>79659</v>
+        <v>91852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665631</v>
+        <v>665801</v>
       </c>
       <c r="R15" t="n">
-        <v>7185482</v>
+        <v>7185555</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,21 +2096,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2127,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880467</v>
+        <v>119880461</v>
       </c>
       <c r="B16" t="n">
-        <v>89269</v>
+        <v>91862</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665967</v>
+        <v>665905</v>
       </c>
       <c r="R16" t="n">
-        <v>7185660</v>
+        <v>7185598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880417</v>
+        <v>119880437</v>
       </c>
       <c r="B17" t="n">
-        <v>77474</v>
+        <v>79659</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2269,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665632</v>
+        <v>665631</v>
       </c>
       <c r="R17" t="n">
-        <v>7185649</v>
+        <v>7185482</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,6 +2300,21 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2331,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880423</v>
+        <v>119880465</v>
       </c>
       <c r="B18" t="n">
-        <v>78279</v>
+        <v>91846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>149</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665584</v>
+        <v>665944</v>
       </c>
       <c r="R18" t="n">
-        <v>7185605</v>
+        <v>7185632</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880449</v>
+        <v>119880440</v>
       </c>
       <c r="B19" t="n">
         <v>78187</v>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665811</v>
+        <v>665733</v>
       </c>
       <c r="R19" t="n">
-        <v>7185566</v>
+        <v>7185520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880409</v>
+        <v>119880418</v>
       </c>
       <c r="B20" t="n">
-        <v>89247</v>
+        <v>91870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,25 +2547,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1596</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665652</v>
+        <v>665618</v>
       </c>
       <c r="R20" t="n">
-        <v>7185701</v>
+        <v>7185647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880448</v>
+        <v>119880446</v>
       </c>
       <c r="B21" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665801</v>
+        <v>665779</v>
       </c>
       <c r="R21" t="n">
-        <v>7185555</v>
+        <v>7185598</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,10 +2739,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880457</v>
+        <v>119880449</v>
       </c>
       <c r="B22" t="n">
-        <v>91870</v>
+        <v>78187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,25 +2751,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665871</v>
+        <v>665811</v>
       </c>
       <c r="R22" t="n">
-        <v>7185570</v>
+        <v>7185566</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880455</v>
+        <v>119880459</v>
       </c>
       <c r="B23" t="n">
-        <v>89292</v>
+        <v>78187</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,25 +2853,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665872</v>
+        <v>665913</v>
       </c>
       <c r="R23" t="n">
-        <v>7185555</v>
+        <v>7185574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880460</v>
+        <v>119880462</v>
       </c>
       <c r="B24" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,25 +2955,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665910</v>
+        <v>665918</v>
       </c>
       <c r="R24" t="n">
-        <v>7185584</v>
+        <v>7185620</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880465</v>
+        <v>119880452</v>
       </c>
       <c r="B25" t="n">
-        <v>91846</v>
+        <v>91844</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,25 +3057,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665944</v>
+        <v>665842</v>
       </c>
       <c r="R25" t="n">
-        <v>7185632</v>
+        <v>7185565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880466</v>
+        <v>119880471</v>
       </c>
       <c r="B26" t="n">
-        <v>91850</v>
+        <v>91846</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,25 +3159,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665966</v>
+        <v>665988</v>
       </c>
       <c r="R26" t="n">
-        <v>7185634</v>
+        <v>7185667</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880456</v>
+        <v>119880433</v>
       </c>
       <c r="B27" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,21 +3265,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665872</v>
+        <v>665516</v>
       </c>
       <c r="R27" t="n">
-        <v>7185563</v>
+        <v>7185504</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880468</v>
+        <v>119880439</v>
       </c>
       <c r="B28" t="n">
-        <v>79160</v>
+        <v>89650</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3367,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665975</v>
+        <v>665731</v>
       </c>
       <c r="R28" t="n">
-        <v>7185666</v>
+        <v>7185521</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880462</v>
+        <v>119880445</v>
       </c>
       <c r="B29" t="n">
-        <v>89269</v>
+        <v>78187</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,25 +3465,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665918</v>
+        <v>665752</v>
       </c>
       <c r="R29" t="n">
-        <v>7185620</v>
+        <v>7185584</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880438</v>
+        <v>119880456</v>
       </c>
       <c r="B30" t="n">
-        <v>91862</v>
+        <v>78187</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,25 +3567,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665723</v>
+        <v>665872</v>
       </c>
       <c r="R30" t="n">
-        <v>7185514</v>
+        <v>7185563</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,7 +3657,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880445</v>
+        <v>119880427</v>
       </c>
       <c r="B31" t="n">
         <v>78187</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665752</v>
+        <v>665573</v>
       </c>
       <c r="R31" t="n">
         <v>7185584</v>
@@ -3759,7 +3759,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880446</v>
+        <v>119880412</v>
       </c>
       <c r="B32" t="n">
         <v>78187</v>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665779</v>
+        <v>665642</v>
       </c>
       <c r="R32" t="n">
-        <v>7185598</v>
+        <v>7185682</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880444</v>
+        <v>119880423</v>
       </c>
       <c r="B33" t="n">
-        <v>89650</v>
+        <v>78279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665746</v>
+        <v>665584</v>
       </c>
       <c r="R33" t="n">
-        <v>7185579</v>
+        <v>7185605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,10 +3963,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880414</v>
+        <v>119880441</v>
       </c>
       <c r="B34" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3979,21 +3979,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665625</v>
+        <v>665740</v>
       </c>
       <c r="R34" t="n">
-        <v>7185661</v>
+        <v>7185522</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880471</v>
+        <v>119880409</v>
       </c>
       <c r="B36" t="n">
-        <v>91846</v>
+        <v>89247</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>149</v>
+        <v>1596</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665988</v>
+        <v>665652</v>
       </c>
       <c r="R36" t="n">
-        <v>7185667</v>
+        <v>7185701</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880429</v>
+        <v>119880398</v>
       </c>
       <c r="B37" t="n">
-        <v>91901</v>
+        <v>89292</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5448</v>
+        <v>6286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665527</v>
+        <v>665837</v>
       </c>
       <c r="R37" t="n">
-        <v>7185533</v>
+        <v>7185742</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880433</v>
+        <v>119880417</v>
       </c>
       <c r="B38" t="n">
-        <v>91852</v>
+        <v>77474</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665516</v>
+        <v>665632</v>
       </c>
       <c r="R38" t="n">
-        <v>7185504</v>
+        <v>7185649</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880430</v>
+        <v>119880473</v>
       </c>
       <c r="B39" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,25 +4485,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665527</v>
+        <v>666000</v>
       </c>
       <c r="R39" t="n">
-        <v>7185533</v>
+        <v>7185668</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880412</v>
+        <v>119880424</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4591,21 +4591,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665642</v>
+        <v>665577</v>
       </c>
       <c r="R40" t="n">
-        <v>7185682</v>
+        <v>7185596</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880431</v>
+        <v>119880425</v>
       </c>
       <c r="B41" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4693,21 +4693,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665509</v>
+        <v>665574</v>
       </c>
       <c r="R41" t="n">
-        <v>7185520</v>
+        <v>7185592</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880442</v>
+        <v>119880430</v>
       </c>
       <c r="B42" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665744</v>
+        <v>665527</v>
       </c>
       <c r="R42" t="n">
-        <v>7185572</v>
+        <v>7185533</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880440</v>
+        <v>119880413</v>
       </c>
       <c r="B43" t="n">
-        <v>78187</v>
+        <v>89292</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,25 +4893,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665733</v>
+        <v>665629</v>
       </c>
       <c r="R43" t="n">
-        <v>7185520</v>
+        <v>7185671</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880441</v>
+        <v>119880451</v>
       </c>
       <c r="B44" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665740</v>
+        <v>665824</v>
       </c>
       <c r="R44" t="n">
-        <v>7185522</v>
+        <v>7185574</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880443</v>
+        <v>119880466</v>
       </c>
       <c r="B45" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,25 +5097,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665746</v>
+        <v>665966</v>
       </c>
       <c r="R45" t="n">
-        <v>7185579</v>
+        <v>7185634</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880425</v>
+        <v>119880467</v>
       </c>
       <c r="B46" t="n">
-        <v>89650</v>
+        <v>89269</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,25 +5199,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>6276</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665574</v>
+        <v>665967</v>
       </c>
       <c r="R46" t="n">
-        <v>7185592</v>
+        <v>7185660</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880447</v>
+        <v>119880458</v>
       </c>
       <c r="B47" t="n">
-        <v>91874</v>
+        <v>89269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,25 +5301,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665779</v>
+        <v>665911</v>
       </c>
       <c r="R47" t="n">
-        <v>7185591</v>
+        <v>7185565</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880450</v>
+        <v>119880453</v>
       </c>
       <c r="B48" t="n">
-        <v>89650</v>
+        <v>91844</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>3100</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665811</v>
+        <v>665867</v>
       </c>
       <c r="R48" t="n">
-        <v>7185566</v>
+        <v>7185548</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880427</v>
+        <v>119880442</v>
       </c>
       <c r="B49" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665573</v>
+        <v>665744</v>
       </c>
       <c r="R49" t="n">
-        <v>7185584</v>
+        <v>7185572</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880452</v>
+        <v>119880429</v>
       </c>
       <c r="B50" t="n">
-        <v>91844</v>
+        <v>91901</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,21 +5611,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3100</v>
+        <v>5448</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665842</v>
+        <v>665527</v>
       </c>
       <c r="R50" t="n">
-        <v>7185565</v>
+        <v>7185533</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880428</v>
+        <v>119880431</v>
       </c>
       <c r="B51" t="n">
-        <v>91902</v>
+        <v>78187</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665530</v>
+        <v>665509</v>
       </c>
       <c r="R51" t="n">
-        <v>7185543</v>
+        <v>7185520</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880411</v>
+        <v>119880414</v>
       </c>
       <c r="B52" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5811,25 +5811,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665645</v>
+        <v>665625</v>
       </c>
       <c r="R52" t="n">
-        <v>7185685</v>
+        <v>7185661</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880472</v>
+        <v>119880443</v>
       </c>
       <c r="B53" t="n">
-        <v>91844</v>
+        <v>91870</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665998</v>
+        <v>665746</v>
       </c>
       <c r="R53" t="n">
-        <v>7185666</v>
+        <v>7185579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880459</v>
+        <v>119880419</v>
       </c>
       <c r="B54" t="n">
         <v>78187</v>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665913</v>
+        <v>665600</v>
       </c>
       <c r="R54" t="n">
-        <v>7185574</v>
+        <v>7185629</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880473</v>
+        <v>119880447</v>
       </c>
       <c r="B55" t="n">
-        <v>91870</v>
+        <v>91874</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6117,25 +6117,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>666000</v>
+        <v>665779</v>
       </c>
       <c r="R55" t="n">
-        <v>7185668</v>
+        <v>7185591</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880454</v>
+        <v>119880468</v>
       </c>
       <c r="B56" t="n">
-        <v>91850</v>
+        <v>79160</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665867</v>
+        <v>665975</v>
       </c>
       <c r="R56" t="n">
-        <v>7185544</v>
+        <v>7185666</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880439</v>
+        <v>119880463</v>
       </c>
       <c r="B57" t="n">
-        <v>89650</v>
+        <v>91844</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1962</v>
+        <v>3100</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665731</v>
+        <v>665918</v>
       </c>
       <c r="R57" t="n">
-        <v>7185521</v>
+        <v>7185620</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880470</v>
+        <v>119880448</v>
       </c>
       <c r="B14" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1920,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665982</v>
+        <v>665801</v>
       </c>
       <c r="R14" t="n">
-        <v>7185672</v>
+        <v>7185555</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880448</v>
+        <v>119880461</v>
       </c>
       <c r="B15" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665801</v>
+        <v>665905</v>
       </c>
       <c r="R15" t="n">
-        <v>7185555</v>
+        <v>7185598</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880461</v>
+        <v>119880470</v>
       </c>
       <c r="B16" t="n">
-        <v>91862</v>
+        <v>89269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665905</v>
+        <v>665982</v>
       </c>
       <c r="R16" t="n">
-        <v>7185598</v>
+        <v>7185672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880430</v>
+        <v>119880413</v>
       </c>
       <c r="B42" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665527</v>
+        <v>665629</v>
       </c>
       <c r="R42" t="n">
-        <v>7185533</v>
+        <v>7185671</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880413</v>
+        <v>119880430</v>
       </c>
       <c r="B43" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4893,25 +4893,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665629</v>
+        <v>665527</v>
       </c>
       <c r="R43" t="n">
-        <v>7185671</v>
+        <v>7185533</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880451</v>
+        <v>119880453</v>
       </c>
       <c r="B44" t="n">
-        <v>78187</v>
+        <v>91844</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665824</v>
+        <v>665867</v>
       </c>
       <c r="R44" t="n">
-        <v>7185574</v>
+        <v>7185548</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880466</v>
+        <v>119880467</v>
       </c>
       <c r="B45" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,25 +5097,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665966</v>
+        <v>665967</v>
       </c>
       <c r="R45" t="n">
-        <v>7185634</v>
+        <v>7185660</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,7 +5187,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880467</v>
+        <v>119880458</v>
       </c>
       <c r="B46" t="n">
         <v>89269</v>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665967</v>
+        <v>665911</v>
       </c>
       <c r="R46" t="n">
-        <v>7185660</v>
+        <v>7185565</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880458</v>
+        <v>119880451</v>
       </c>
       <c r="B47" t="n">
-        <v>89269</v>
+        <v>78187</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,25 +5301,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665911</v>
+        <v>665824</v>
       </c>
       <c r="R47" t="n">
-        <v>7185565</v>
+        <v>7185574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880453</v>
+        <v>119880466</v>
       </c>
       <c r="B48" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665867</v>
+        <v>665966</v>
       </c>
       <c r="R48" t="n">
-        <v>7185548</v>
+        <v>7185634</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880442</v>
+        <v>119880431</v>
       </c>
       <c r="B49" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665744</v>
+        <v>665509</v>
       </c>
       <c r="R49" t="n">
-        <v>7185572</v>
+        <v>7185520</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880429</v>
+        <v>119880414</v>
       </c>
       <c r="B50" t="n">
-        <v>91901</v>
+        <v>78187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5611,21 +5611,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665527</v>
+        <v>665625</v>
       </c>
       <c r="R50" t="n">
-        <v>7185533</v>
+        <v>7185661</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880431</v>
+        <v>119880442</v>
       </c>
       <c r="B51" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665509</v>
+        <v>665744</v>
       </c>
       <c r="R51" t="n">
-        <v>7185520</v>
+        <v>7185572</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880414</v>
+        <v>119880429</v>
       </c>
       <c r="B52" t="n">
-        <v>78187</v>
+        <v>91901</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665625</v>
+        <v>665527</v>
       </c>
       <c r="R52" t="n">
-        <v>7185661</v>
+        <v>7185533</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880468</v>
+        <v>119880463</v>
       </c>
       <c r="B56" t="n">
-        <v>79160</v>
+        <v>91844</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665975</v>
+        <v>665918</v>
       </c>
       <c r="R56" t="n">
-        <v>7185666</v>
+        <v>7185620</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880463</v>
+        <v>119880468</v>
       </c>
       <c r="B57" t="n">
-        <v>91844</v>
+        <v>79160</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3100</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665918</v>
+        <v>665975</v>
       </c>
       <c r="R57" t="n">
-        <v>7185620</v>
+        <v>7185666</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880438</v>
+        <v>119880411</v>
       </c>
       <c r="B3" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665723</v>
+        <v>665645</v>
       </c>
       <c r="R3" t="n">
-        <v>7185514</v>
+        <v>7185685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880411</v>
+        <v>119880417</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>77474</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665645</v>
+        <v>665632</v>
       </c>
       <c r="R4" t="n">
-        <v>7185685</v>
+        <v>7185649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880457</v>
+        <v>119880419</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
+        <v>78187</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665871</v>
+        <v>665600</v>
       </c>
       <c r="R5" t="n">
-        <v>7185570</v>
+        <v>7185629</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880450</v>
+        <v>119880412</v>
       </c>
       <c r="B6" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665811</v>
+        <v>665642</v>
       </c>
       <c r="R6" t="n">
-        <v>7185566</v>
+        <v>7185682</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880428</v>
+        <v>119880433</v>
       </c>
       <c r="B7" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665530</v>
+        <v>665516</v>
       </c>
       <c r="R7" t="n">
-        <v>7185543</v>
+        <v>7185504</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880460</v>
+        <v>119880398</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665910</v>
+        <v>665837</v>
       </c>
       <c r="R8" t="n">
-        <v>7185584</v>
+        <v>7185742</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880455</v>
+        <v>119880429</v>
       </c>
       <c r="B9" t="n">
-        <v>89292</v>
+        <v>91901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6286</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665872</v>
+        <v>665527</v>
       </c>
       <c r="R9" t="n">
-        <v>7185555</v>
+        <v>7185533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880410</v>
+        <v>119880470</v>
       </c>
       <c r="B10" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1512,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665646</v>
+        <v>665982</v>
       </c>
       <c r="R10" t="n">
-        <v>7185686</v>
+        <v>7185672</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880454</v>
+        <v>119880430</v>
       </c>
       <c r="B11" t="n">
         <v>91850</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665867</v>
+        <v>665527</v>
       </c>
       <c r="R11" t="n">
-        <v>7185544</v>
+        <v>7185533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880444</v>
+        <v>119880473</v>
       </c>
       <c r="B12" t="n">
-        <v>89650</v>
+        <v>91870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1716,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665746</v>
+        <v>666000</v>
       </c>
       <c r="R12" t="n">
-        <v>7185579</v>
+        <v>7185668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880472</v>
+        <v>119880431</v>
       </c>
       <c r="B13" t="n">
-        <v>91844</v>
+        <v>78187</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665998</v>
+        <v>665509</v>
       </c>
       <c r="R13" t="n">
-        <v>7185666</v>
+        <v>7185520</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880448</v>
+        <v>119880439</v>
       </c>
       <c r="B14" t="n">
-        <v>91852</v>
+        <v>89650</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665801</v>
+        <v>665731</v>
       </c>
       <c r="R14" t="n">
-        <v>7185555</v>
+        <v>7185521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880461</v>
+        <v>119880440</v>
       </c>
       <c r="B15" t="n">
-        <v>91862</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665905</v>
+        <v>665733</v>
       </c>
       <c r="R15" t="n">
-        <v>7185598</v>
+        <v>7185520</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880470</v>
+        <v>119880441</v>
       </c>
       <c r="B16" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665982</v>
+        <v>665740</v>
       </c>
       <c r="R16" t="n">
-        <v>7185672</v>
+        <v>7185522</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880437</v>
+        <v>119880460</v>
       </c>
       <c r="B17" t="n">
-        <v>79659</v>
+        <v>91850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665631</v>
+        <v>665910</v>
       </c>
       <c r="R17" t="n">
-        <v>7185482</v>
+        <v>7185584</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,21 +2300,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2331,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880465</v>
+        <v>119880454</v>
       </c>
       <c r="B18" t="n">
-        <v>91846</v>
+        <v>91850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,25 +2328,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665944</v>
+        <v>665867</v>
       </c>
       <c r="R18" t="n">
-        <v>7185632</v>
+        <v>7185544</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880440</v>
+        <v>119880453</v>
       </c>
       <c r="B19" t="n">
-        <v>78187</v>
+        <v>91844</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2449,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2473,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665733</v>
+        <v>665867</v>
       </c>
       <c r="R19" t="n">
-        <v>7185520</v>
+        <v>7185548</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880418</v>
+        <v>119880468</v>
       </c>
       <c r="B20" t="n">
-        <v>91870</v>
+        <v>79160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2575,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665618</v>
+        <v>665975</v>
       </c>
       <c r="R20" t="n">
-        <v>7185647</v>
+        <v>7185666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2622,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880446</v>
+        <v>119880449</v>
       </c>
       <c r="B21" t="n">
         <v>78187</v>
@@ -2677,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665779</v>
+        <v>665811</v>
       </c>
       <c r="R21" t="n">
-        <v>7185598</v>
+        <v>7185566</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880449</v>
+        <v>119880443</v>
       </c>
       <c r="B22" t="n">
-        <v>78187</v>
+        <v>91870</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2751,25 +2736,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665811</v>
+        <v>665746</v>
       </c>
       <c r="R22" t="n">
-        <v>7185566</v>
+        <v>7185579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880459</v>
+        <v>119880467</v>
       </c>
       <c r="B23" t="n">
-        <v>78187</v>
+        <v>89269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,25 +2838,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2881,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665913</v>
+        <v>665967</v>
       </c>
       <c r="R23" t="n">
-        <v>7185574</v>
+        <v>7185660</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880462</v>
+        <v>119880455</v>
       </c>
       <c r="B24" t="n">
-        <v>89269</v>
+        <v>89292</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>6286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665918</v>
+        <v>665872</v>
       </c>
       <c r="R24" t="n">
-        <v>7185620</v>
+        <v>7185555</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880452</v>
+        <v>119880461</v>
       </c>
       <c r="B25" t="n">
-        <v>91844</v>
+        <v>91862</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3057,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3100</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3085,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665842</v>
+        <v>665905</v>
       </c>
       <c r="R25" t="n">
-        <v>7185565</v>
+        <v>7185598</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880471</v>
+        <v>119880410</v>
       </c>
       <c r="B26" t="n">
-        <v>91846</v>
+        <v>91850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3159,25 +3144,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>149</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665988</v>
+        <v>665646</v>
       </c>
       <c r="R26" t="n">
-        <v>7185667</v>
+        <v>7185686</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880433</v>
+        <v>119880437</v>
       </c>
       <c r="B27" t="n">
-        <v>91852</v>
+        <v>79659</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3261,25 +3246,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665516</v>
+        <v>665631</v>
       </c>
       <c r="R27" t="n">
-        <v>7185504</v>
+        <v>7185482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,6 +3320,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3351,10 +3351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880439</v>
+        <v>119880462</v>
       </c>
       <c r="B28" t="n">
-        <v>89650</v>
+        <v>89269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3363,25 +3363,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>6276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665731</v>
+        <v>665918</v>
       </c>
       <c r="R28" t="n">
-        <v>7185521</v>
+        <v>7185620</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880445</v>
+        <v>119880438</v>
       </c>
       <c r="B29" t="n">
-        <v>78187</v>
+        <v>91862</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,25 +3465,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665752</v>
+        <v>665723</v>
       </c>
       <c r="R29" t="n">
-        <v>7185584</v>
+        <v>7185514</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880427</v>
+        <v>119880409</v>
       </c>
       <c r="B31" t="n">
-        <v>78187</v>
+        <v>89247</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,25 +3669,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>1596</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665573</v>
+        <v>665652</v>
       </c>
       <c r="R31" t="n">
-        <v>7185584</v>
+        <v>7185701</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880412</v>
+        <v>119880450</v>
       </c>
       <c r="B32" t="n">
-        <v>78187</v>
+        <v>89650</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665642</v>
+        <v>665811</v>
       </c>
       <c r="R32" t="n">
-        <v>7185682</v>
+        <v>7185566</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880423</v>
+        <v>119880428</v>
       </c>
       <c r="B33" t="n">
-        <v>78279</v>
+        <v>91902</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665584</v>
+        <v>665530</v>
       </c>
       <c r="R33" t="n">
-        <v>7185605</v>
+        <v>7185543</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,7 +3963,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880441</v>
+        <v>119880442</v>
       </c>
       <c r="B34" t="n">
         <v>91852</v>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665740</v>
+        <v>665744</v>
       </c>
       <c r="R34" t="n">
-        <v>7185522</v>
+        <v>7185572</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4065,10 +4065,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880464</v>
+        <v>119880445</v>
       </c>
       <c r="B35" t="n">
-        <v>91870</v>
+        <v>78187</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4077,25 +4077,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665922</v>
+        <v>665752</v>
       </c>
       <c r="R35" t="n">
-        <v>7185624</v>
+        <v>7185584</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880409</v>
+        <v>119880447</v>
       </c>
       <c r="B36" t="n">
-        <v>89247</v>
+        <v>91874</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4179,25 +4179,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1596</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665652</v>
+        <v>665779</v>
       </c>
       <c r="R36" t="n">
-        <v>7185701</v>
+        <v>7185591</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880398</v>
+        <v>119880448</v>
       </c>
       <c r="B37" t="n">
-        <v>89292</v>
+        <v>91852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665837</v>
+        <v>665801</v>
       </c>
       <c r="R37" t="n">
-        <v>7185742</v>
+        <v>7185555</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880417</v>
+        <v>119880466</v>
       </c>
       <c r="B38" t="n">
-        <v>77474</v>
+        <v>91850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6487</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665632</v>
+        <v>665966</v>
       </c>
       <c r="R38" t="n">
-        <v>7185649</v>
+        <v>7185634</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880473</v>
+        <v>119880463</v>
       </c>
       <c r="B39" t="n">
-        <v>91870</v>
+        <v>91844</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4485,25 +4485,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>666000</v>
+        <v>665918</v>
       </c>
       <c r="R39" t="n">
-        <v>7185668</v>
+        <v>7185620</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,10 +4677,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880425</v>
+        <v>119880446</v>
       </c>
       <c r="B41" t="n">
-        <v>89650</v>
+        <v>78187</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4693,21 +4693,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665574</v>
+        <v>665779</v>
       </c>
       <c r="R41" t="n">
-        <v>7185592</v>
+        <v>7185598</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880413</v>
+        <v>119880414</v>
       </c>
       <c r="B42" t="n">
-        <v>89292</v>
+        <v>78187</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6286</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665629</v>
+        <v>665625</v>
       </c>
       <c r="R42" t="n">
-        <v>7185671</v>
+        <v>7185661</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880430</v>
+        <v>119880444</v>
       </c>
       <c r="B43" t="n">
-        <v>91850</v>
+        <v>89650</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665527</v>
+        <v>665746</v>
       </c>
       <c r="R43" t="n">
-        <v>7185533</v>
+        <v>7185579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880453</v>
+        <v>119880457</v>
       </c>
       <c r="B44" t="n">
-        <v>91844</v>
+        <v>91870</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +4995,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3100</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665867</v>
+        <v>665871</v>
       </c>
       <c r="R44" t="n">
-        <v>7185548</v>
+        <v>7185570</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880467</v>
+        <v>119880464</v>
       </c>
       <c r="B45" t="n">
-        <v>89269</v>
+        <v>91870</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,25 +5097,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665967</v>
+        <v>665922</v>
       </c>
       <c r="R45" t="n">
-        <v>7185660</v>
+        <v>7185624</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880458</v>
+        <v>119880459</v>
       </c>
       <c r="B46" t="n">
-        <v>89269</v>
+        <v>78187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5199,25 +5199,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665911</v>
+        <v>665913</v>
       </c>
       <c r="R46" t="n">
-        <v>7185565</v>
+        <v>7185574</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880451</v>
+        <v>119880418</v>
       </c>
       <c r="B47" t="n">
-        <v>78187</v>
+        <v>91870</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,25 +5301,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665824</v>
+        <v>665618</v>
       </c>
       <c r="R47" t="n">
-        <v>7185574</v>
+        <v>7185647</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880466</v>
+        <v>119880452</v>
       </c>
       <c r="B48" t="n">
-        <v>91850</v>
+        <v>91844</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665966</v>
+        <v>665842</v>
       </c>
       <c r="R48" t="n">
-        <v>7185634</v>
+        <v>7185565</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880431</v>
+        <v>119880472</v>
       </c>
       <c r="B49" t="n">
-        <v>78187</v>
+        <v>91844</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>3100</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665509</v>
+        <v>665998</v>
       </c>
       <c r="R49" t="n">
-        <v>7185520</v>
+        <v>7185666</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880414</v>
+        <v>119880458</v>
       </c>
       <c r="B50" t="n">
-        <v>78187</v>
+        <v>89269</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,25 +5607,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665625</v>
+        <v>665911</v>
       </c>
       <c r="R50" t="n">
-        <v>7185661</v>
+        <v>7185565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880442</v>
+        <v>119880471</v>
       </c>
       <c r="B51" t="n">
-        <v>91852</v>
+        <v>91846</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5709,25 +5709,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4362</v>
+        <v>149</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665744</v>
+        <v>665988</v>
       </c>
       <c r="R51" t="n">
-        <v>7185572</v>
+        <v>7185667</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880429</v>
+        <v>119880425</v>
       </c>
       <c r="B52" t="n">
-        <v>91901</v>
+        <v>89650</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5448</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665527</v>
+        <v>665574</v>
       </c>
       <c r="R52" t="n">
-        <v>7185533</v>
+        <v>7185592</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880443</v>
+        <v>119880413</v>
       </c>
       <c r="B53" t="n">
-        <v>91870</v>
+        <v>89292</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665746</v>
+        <v>665629</v>
       </c>
       <c r="R53" t="n">
-        <v>7185579</v>
+        <v>7185671</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880419</v>
+        <v>119880465</v>
       </c>
       <c r="B54" t="n">
-        <v>78187</v>
+        <v>91846</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665600</v>
+        <v>665944</v>
       </c>
       <c r="R54" t="n">
-        <v>7185629</v>
+        <v>7185632</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880447</v>
+        <v>119880423</v>
       </c>
       <c r="B55" t="n">
-        <v>91874</v>
+        <v>78279</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6121,21 +6121,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665779</v>
+        <v>665584</v>
       </c>
       <c r="R55" t="n">
-        <v>7185591</v>
+        <v>7185605</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880463</v>
+        <v>119880427</v>
       </c>
       <c r="B56" t="n">
-        <v>91844</v>
+        <v>78187</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665918</v>
+        <v>665573</v>
       </c>
       <c r="R56" t="n">
-        <v>7185620</v>
+        <v>7185584</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880468</v>
+        <v>119880451</v>
       </c>
       <c r="B57" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6325,21 +6325,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665975</v>
+        <v>665824</v>
       </c>
       <c r="R57" t="n">
-        <v>7185666</v>
+        <v>7185574</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880411</v>
+        <v>119880451</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665645</v>
+        <v>665824</v>
       </c>
       <c r="R3" t="n">
-        <v>7185685</v>
+        <v>7185574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880419</v>
+        <v>119880423</v>
       </c>
       <c r="B5" t="n">
-        <v>78187</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665600</v>
+        <v>665584</v>
       </c>
       <c r="R5" t="n">
-        <v>7185629</v>
+        <v>7185605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880412</v>
+        <v>119880411</v>
       </c>
       <c r="B6" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665642</v>
+        <v>665645</v>
       </c>
       <c r="R6" t="n">
-        <v>7185682</v>
+        <v>7185685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880433</v>
+        <v>119880453</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665516</v>
+        <v>665867</v>
       </c>
       <c r="R7" t="n">
-        <v>7185504</v>
+        <v>7185548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880398</v>
+        <v>119880410</v>
       </c>
       <c r="B8" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665837</v>
+        <v>665646</v>
       </c>
       <c r="R8" t="n">
-        <v>7185742</v>
+        <v>7185686</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880429</v>
+        <v>119880464</v>
       </c>
       <c r="B9" t="n">
-        <v>91901</v>
+        <v>91870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665527</v>
+        <v>665922</v>
       </c>
       <c r="R9" t="n">
-        <v>7185533</v>
+        <v>7185624</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880430</v>
+        <v>119880467</v>
       </c>
       <c r="B11" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665527</v>
+        <v>665967</v>
       </c>
       <c r="R11" t="n">
-        <v>7185533</v>
+        <v>7185660</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880473</v>
+        <v>119880418</v>
       </c>
       <c r="B12" t="n">
         <v>91870</v>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666000</v>
+        <v>665618</v>
       </c>
       <c r="R12" t="n">
-        <v>7185668</v>
+        <v>7185647</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880431</v>
+        <v>119880457</v>
       </c>
       <c r="B13" t="n">
-        <v>78187</v>
+        <v>91870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665509</v>
+        <v>665871</v>
       </c>
       <c r="R13" t="n">
-        <v>7185520</v>
+        <v>7185570</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880439</v>
+        <v>119880447</v>
       </c>
       <c r="B14" t="n">
-        <v>89650</v>
+        <v>91874</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665731</v>
+        <v>665779</v>
       </c>
       <c r="R14" t="n">
-        <v>7185521</v>
+        <v>7185591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880440</v>
+        <v>119880412</v>
       </c>
       <c r="B15" t="n">
         <v>78187</v>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665733</v>
+        <v>665642</v>
       </c>
       <c r="R15" t="n">
-        <v>7185520</v>
+        <v>7185682</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880441</v>
+        <v>119880445</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665740</v>
+        <v>665752</v>
       </c>
       <c r="R16" t="n">
-        <v>7185522</v>
+        <v>7185584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880460</v>
+        <v>119880439</v>
       </c>
       <c r="B17" t="n">
-        <v>91850</v>
+        <v>89650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665910</v>
+        <v>665731</v>
       </c>
       <c r="R17" t="n">
-        <v>7185584</v>
+        <v>7185521</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880454</v>
+        <v>119880472</v>
       </c>
       <c r="B18" t="n">
-        <v>91850</v>
+        <v>91844</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665867</v>
+        <v>665998</v>
       </c>
       <c r="R18" t="n">
-        <v>7185544</v>
+        <v>7185666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880453</v>
+        <v>119880424</v>
       </c>
       <c r="B19" t="n">
-        <v>91844</v>
+        <v>91852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665867</v>
+        <v>665577</v>
       </c>
       <c r="R19" t="n">
-        <v>7185548</v>
+        <v>7185596</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880468</v>
+        <v>119880428</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665975</v>
+        <v>665530</v>
       </c>
       <c r="R20" t="n">
-        <v>7185666</v>
+        <v>7185543</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880449</v>
+        <v>119880398</v>
       </c>
       <c r="B21" t="n">
-        <v>78187</v>
+        <v>89292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2634,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665811</v>
+        <v>665837</v>
       </c>
       <c r="R21" t="n">
-        <v>7185566</v>
+        <v>7185742</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880443</v>
+        <v>119880437</v>
       </c>
       <c r="B22" t="n">
-        <v>91870</v>
+        <v>79659</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665746</v>
+        <v>665631</v>
       </c>
       <c r="R22" t="n">
-        <v>7185579</v>
+        <v>7185482</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,6 +2810,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2826,10 +2841,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880467</v>
+        <v>119880466</v>
       </c>
       <c r="B23" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,25 +2853,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2881,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665967</v>
+        <v>665966</v>
       </c>
       <c r="R23" t="n">
-        <v>7185660</v>
+        <v>7185634</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880455</v>
+        <v>119880454</v>
       </c>
       <c r="B24" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,25 +2955,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2983,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665872</v>
+        <v>665867</v>
       </c>
       <c r="R24" t="n">
-        <v>7185555</v>
+        <v>7185544</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3045,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880461</v>
+        <v>119880425</v>
       </c>
       <c r="B25" t="n">
-        <v>91862</v>
+        <v>89650</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3057,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665905</v>
+        <v>665574</v>
       </c>
       <c r="R25" t="n">
-        <v>7185598</v>
+        <v>7185592</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3147,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880410</v>
+        <v>119880427</v>
       </c>
       <c r="B26" t="n">
-        <v>91850</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3148,21 +3163,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3187,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665646</v>
+        <v>665573</v>
       </c>
       <c r="R26" t="n">
-        <v>7185686</v>
+        <v>7185584</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3249,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880437</v>
+        <v>119880463</v>
       </c>
       <c r="B27" t="n">
-        <v>79659</v>
+        <v>91844</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3261,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>3100</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3289,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665631</v>
+        <v>665918</v>
       </c>
       <c r="R27" t="n">
-        <v>7185482</v>
+        <v>7185620</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3320,21 +3335,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3351,10 +3351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880462</v>
+        <v>119880465</v>
       </c>
       <c r="B28" t="n">
-        <v>89269</v>
+        <v>91846</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3367,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6276</v>
+        <v>149</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665918</v>
+        <v>665944</v>
       </c>
       <c r="R28" t="n">
-        <v>7185620</v>
+        <v>7185632</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,10 +3453,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880438</v>
+        <v>119880473</v>
       </c>
       <c r="B29" t="n">
-        <v>91862</v>
+        <v>91870</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3465,25 +3465,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>665723</v>
+        <v>666000</v>
       </c>
       <c r="R29" t="n">
-        <v>7185514</v>
+        <v>7185668</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880456</v>
+        <v>119880455</v>
       </c>
       <c r="B30" t="n">
-        <v>78187</v>
+        <v>89292</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3567,25 +3567,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3598,7 +3598,7 @@
         <v>665872</v>
       </c>
       <c r="R30" t="n">
-        <v>7185563</v>
+        <v>7185555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880409</v>
+        <v>119880456</v>
       </c>
       <c r="B31" t="n">
-        <v>89247</v>
+        <v>78187</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3669,25 +3669,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1596</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665652</v>
+        <v>665872</v>
       </c>
       <c r="R31" t="n">
-        <v>7185701</v>
+        <v>7185563</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880450</v>
+        <v>119880452</v>
       </c>
       <c r="B32" t="n">
-        <v>89650</v>
+        <v>91844</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3775,21 +3775,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>3100</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665811</v>
+        <v>665842</v>
       </c>
       <c r="R32" t="n">
-        <v>7185566</v>
+        <v>7185565</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3861,10 +3861,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880428</v>
+        <v>119880446</v>
       </c>
       <c r="B33" t="n">
-        <v>91902</v>
+        <v>78187</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3877,21 +3877,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665530</v>
+        <v>665779</v>
       </c>
       <c r="R33" t="n">
-        <v>7185543</v>
+        <v>7185598</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4065,7 +4065,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880445</v>
+        <v>119880449</v>
       </c>
       <c r="B35" t="n">
         <v>78187</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665752</v>
+        <v>665811</v>
       </c>
       <c r="R35" t="n">
-        <v>7185584</v>
+        <v>7185566</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880447</v>
+        <v>119880414</v>
       </c>
       <c r="B36" t="n">
-        <v>91874</v>
+        <v>78187</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4183,21 +4183,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665779</v>
+        <v>665625</v>
       </c>
       <c r="R36" t="n">
-        <v>7185591</v>
+        <v>7185661</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880448</v>
+        <v>119880444</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>89650</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,21 +4285,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665801</v>
+        <v>665746</v>
       </c>
       <c r="R37" t="n">
-        <v>7185555</v>
+        <v>7185579</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,10 +4371,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880466</v>
+        <v>119880461</v>
       </c>
       <c r="B38" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4383,25 +4383,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665966</v>
+        <v>665905</v>
       </c>
       <c r="R38" t="n">
-        <v>7185634</v>
+        <v>7185598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880463</v>
+        <v>119880450</v>
       </c>
       <c r="B39" t="n">
-        <v>91844</v>
+        <v>89650</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3100</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665918</v>
+        <v>665811</v>
       </c>
       <c r="R39" t="n">
-        <v>7185620</v>
+        <v>7185566</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4575,10 +4575,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880424</v>
+        <v>119880459</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>78187</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4591,21 +4591,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665577</v>
+        <v>665913</v>
       </c>
       <c r="R40" t="n">
-        <v>7185596</v>
+        <v>7185574</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880446</v>
+        <v>119880419</v>
       </c>
       <c r="B41" t="n">
         <v>78187</v>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665779</v>
+        <v>665600</v>
       </c>
       <c r="R41" t="n">
-        <v>7185598</v>
+        <v>7185629</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880414</v>
+        <v>119880438</v>
       </c>
       <c r="B42" t="n">
-        <v>78187</v>
+        <v>91862</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4791,25 +4791,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665625</v>
+        <v>665723</v>
       </c>
       <c r="R42" t="n">
-        <v>7185661</v>
+        <v>7185514</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,10 +4881,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880444</v>
+        <v>119880460</v>
       </c>
       <c r="B43" t="n">
-        <v>89650</v>
+        <v>91850</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665746</v>
+        <v>665910</v>
       </c>
       <c r="R43" t="n">
-        <v>7185579</v>
+        <v>7185584</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880457</v>
+        <v>119880430</v>
       </c>
       <c r="B44" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4995,25 +4995,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665871</v>
+        <v>665527</v>
       </c>
       <c r="R44" t="n">
-        <v>7185570</v>
+        <v>7185533</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880464</v>
+        <v>119880468</v>
       </c>
       <c r="B45" t="n">
-        <v>91870</v>
+        <v>79160</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5097,25 +5097,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665922</v>
+        <v>665975</v>
       </c>
       <c r="R45" t="n">
-        <v>7185624</v>
+        <v>7185666</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880459</v>
+        <v>119880433</v>
       </c>
       <c r="B46" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5203,21 +5203,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665913</v>
+        <v>665516</v>
       </c>
       <c r="R46" t="n">
-        <v>7185574</v>
+        <v>7185504</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,10 +5289,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880418</v>
+        <v>119880413</v>
       </c>
       <c r="B47" t="n">
-        <v>91870</v>
+        <v>89292</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5301,25 +5301,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5329,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665618</v>
+        <v>665629</v>
       </c>
       <c r="R47" t="n">
-        <v>7185647</v>
+        <v>7185671</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,10 +5391,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880452</v>
+        <v>119880458</v>
       </c>
       <c r="B48" t="n">
-        <v>91844</v>
+        <v>89269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5403,25 +5403,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665842</v>
+        <v>665911</v>
       </c>
       <c r="R48" t="n">
         <v>7185565</v>
@@ -5493,10 +5493,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880472</v>
+        <v>119880471</v>
       </c>
       <c r="B49" t="n">
-        <v>91844</v>
+        <v>91846</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5505,25 +5505,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3100</v>
+        <v>149</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665998</v>
+        <v>665988</v>
       </c>
       <c r="R49" t="n">
-        <v>7185666</v>
+        <v>7185667</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5595,10 +5595,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880458</v>
+        <v>119880431</v>
       </c>
       <c r="B50" t="n">
-        <v>89269</v>
+        <v>78187</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5607,25 +5607,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665911</v>
+        <v>665509</v>
       </c>
       <c r="R50" t="n">
-        <v>7185565</v>
+        <v>7185520</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5697,10 +5697,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880471</v>
+        <v>119880409</v>
       </c>
       <c r="B51" t="n">
-        <v>91846</v>
+        <v>89247</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5713,21 +5713,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>149</v>
+        <v>1596</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665988</v>
+        <v>665652</v>
       </c>
       <c r="R51" t="n">
-        <v>7185667</v>
+        <v>7185701</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880425</v>
+        <v>119880441</v>
       </c>
       <c r="B52" t="n">
-        <v>89650</v>
+        <v>91852</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5815,21 +5815,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665574</v>
+        <v>665740</v>
       </c>
       <c r="R52" t="n">
-        <v>7185592</v>
+        <v>7185522</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,10 +5901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880413</v>
+        <v>119880443</v>
       </c>
       <c r="B53" t="n">
-        <v>89292</v>
+        <v>91870</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5913,25 +5913,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6286</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665629</v>
+        <v>665746</v>
       </c>
       <c r="R53" t="n">
-        <v>7185671</v>
+        <v>7185579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,10 +6003,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880465</v>
+        <v>119880440</v>
       </c>
       <c r="B54" t="n">
-        <v>91846</v>
+        <v>78187</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6015,25 +6015,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665944</v>
+        <v>665733</v>
       </c>
       <c r="R54" t="n">
-        <v>7185632</v>
+        <v>7185520</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6105,10 +6105,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880423</v>
+        <v>119880448</v>
       </c>
       <c r="B55" t="n">
-        <v>78279</v>
+        <v>91852</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6121,21 +6121,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665584</v>
+        <v>665801</v>
       </c>
       <c r="R55" t="n">
-        <v>7185605</v>
+        <v>7185555</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880427</v>
+        <v>119880429</v>
       </c>
       <c r="B56" t="n">
-        <v>78187</v>
+        <v>91901</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665573</v>
+        <v>665527</v>
       </c>
       <c r="R56" t="n">
-        <v>7185584</v>
+        <v>7185533</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,10 +6309,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880451</v>
+        <v>119880462</v>
       </c>
       <c r="B57" t="n">
-        <v>78187</v>
+        <v>89269</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6321,25 +6321,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665824</v>
+        <v>665918</v>
       </c>
       <c r="R57" t="n">
-        <v>7185574</v>
+        <v>7185620</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675822</v>
+        <v>119880465</v>
       </c>
       <c r="B2" t="n">
-        <v>78229</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Peck) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falträsk, Ly lm</t>
+          <t>Nyängesbäckberget, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665893</v>
+        <v>665944</v>
       </c>
       <c r="R2" t="n">
-        <v>7185443</v>
+        <v>7185632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Emil Larsson, Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119880451</v>
+        <v>119880471</v>
       </c>
       <c r="B3" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665824</v>
+        <v>665988</v>
       </c>
       <c r="R3" t="n">
-        <v>7185574</v>
+        <v>7185667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119880417</v>
+        <v>119880481</v>
       </c>
       <c r="B4" t="n">
-        <v>77474</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>149</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665632</v>
+        <v>666027</v>
       </c>
       <c r="R4" t="n">
-        <v>7185649</v>
+        <v>7185701</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119880423</v>
+        <v>119880412</v>
       </c>
       <c r="B5" t="n">
-        <v>78279</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665584</v>
+        <v>665642</v>
       </c>
       <c r="R5" t="n">
-        <v>7185605</v>
+        <v>7185682</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119880411</v>
+        <v>119880414</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665645</v>
+        <v>665625</v>
       </c>
       <c r="R6" t="n">
-        <v>7185685</v>
+        <v>7185661</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119880453</v>
+        <v>119880419</v>
       </c>
       <c r="B7" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665867</v>
+        <v>665600</v>
       </c>
       <c r="R7" t="n">
-        <v>7185548</v>
+        <v>7185629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119880410</v>
+        <v>119880427</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665646</v>
+        <v>665573</v>
       </c>
       <c r="R8" t="n">
-        <v>7185686</v>
+        <v>7185584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119880464</v>
+        <v>119880431</v>
       </c>
       <c r="B9" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665922</v>
+        <v>665509</v>
       </c>
       <c r="R9" t="n">
-        <v>7185624</v>
+        <v>7185520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119880470</v>
+        <v>119880434</v>
       </c>
       <c r="B10" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665982</v>
+        <v>665599</v>
       </c>
       <c r="R10" t="n">
-        <v>7185672</v>
+        <v>7185503</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,44 +1541,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119880467</v>
+        <v>119880440</v>
       </c>
       <c r="B11" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665967</v>
+        <v>665733</v>
       </c>
       <c r="R11" t="n">
-        <v>7185660</v>
+        <v>7185520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,44 +1638,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119880418</v>
+        <v>119880445</v>
       </c>
       <c r="B12" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665618</v>
+        <v>665752</v>
       </c>
       <c r="R12" t="n">
-        <v>7185647</v>
+        <v>7185584</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,44 +1735,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119880457</v>
+        <v>119880446</v>
       </c>
       <c r="B13" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665871</v>
+        <v>665779</v>
       </c>
       <c r="R13" t="n">
-        <v>7185570</v>
+        <v>7185598</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,22 +1832,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119880447</v>
+        <v>119880449</v>
       </c>
       <c r="B14" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665779</v>
+        <v>665811</v>
       </c>
       <c r="R14" t="n">
-        <v>7185591</v>
+        <v>7185566</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,22 +1929,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119880412</v>
+        <v>119880451</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665642</v>
+        <v>665824</v>
       </c>
       <c r="R15" t="n">
-        <v>7185682</v>
+        <v>7185574</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,22 +2026,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119880445</v>
+        <v>119880456</v>
       </c>
       <c r="B16" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>665752</v>
+        <v>665872</v>
       </c>
       <c r="R16" t="n">
-        <v>7185584</v>
+        <v>7185563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,22 +2123,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119880439</v>
+        <v>119880459</v>
       </c>
       <c r="B17" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>665731</v>
+        <v>665913</v>
       </c>
       <c r="R17" t="n">
-        <v>7185521</v>
+        <v>7185574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,22 +2220,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119880472</v>
+        <v>119880476</v>
       </c>
       <c r="B18" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>665998</v>
+        <v>666018</v>
       </c>
       <c r="R18" t="n">
-        <v>7185666</v>
+        <v>7185712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,37 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119880424</v>
+        <v>119880406</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>665577</v>
+        <v>665673</v>
       </c>
       <c r="R19" t="n">
-        <v>7185596</v>
+        <v>7185728</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119880428</v>
+        <v>119880409</v>
       </c>
       <c r="B20" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>1596</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>665530</v>
+        <v>665652</v>
       </c>
       <c r="R20" t="n">
-        <v>7185543</v>
+        <v>7185701</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119880398</v>
+        <v>119880407</v>
       </c>
       <c r="B21" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6286</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>665837</v>
+        <v>665658</v>
       </c>
       <c r="R21" t="n">
-        <v>7185742</v>
+        <v>7185719</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119880437</v>
+        <v>119880425</v>
       </c>
       <c r="B22" t="n">
-        <v>79659</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>665631</v>
+        <v>665574</v>
       </c>
       <c r="R22" t="n">
-        <v>7185482</v>
+        <v>7185592</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,21 +2696,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2841,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119880466</v>
+        <v>119880439</v>
       </c>
       <c r="B23" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2881,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>665966</v>
+        <v>665731</v>
       </c>
       <c r="R23" t="n">
-        <v>7185634</v>
+        <v>7185521</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2936,22 +2802,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119880454</v>
+        <v>119880444</v>
       </c>
       <c r="B24" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2959,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2983,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>665867</v>
+        <v>665746</v>
       </c>
       <c r="R24" t="n">
-        <v>7185544</v>
+        <v>7185579</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3038,22 +2899,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119880425</v>
+        <v>119880450</v>
       </c>
       <c r="B25" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3085,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>665574</v>
+        <v>665811</v>
       </c>
       <c r="R25" t="n">
-        <v>7185592</v>
+        <v>7185566</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3140,44 +2996,39 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119880427</v>
+        <v>119880447</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3187,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>665573</v>
+        <v>665779</v>
       </c>
       <c r="R26" t="n">
-        <v>7185584</v>
+        <v>7185591</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,22 +3093,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119880463</v>
+        <v>119880452</v>
       </c>
       <c r="B27" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3274,12 +3120,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3289,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>665918</v>
+        <v>665842</v>
       </c>
       <c r="R27" t="n">
-        <v>7185620</v>
+        <v>7185565</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3344,44 +3190,39 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119880465</v>
+        <v>119880453</v>
       </c>
       <c r="B28" t="n">
-        <v>91846</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>149</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3391,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>665944</v>
+        <v>665867</v>
       </c>
       <c r="R28" t="n">
-        <v>7185632</v>
+        <v>7185548</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3446,44 +3287,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119880473</v>
+        <v>119880463</v>
       </c>
       <c r="B29" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3493,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>666000</v>
+        <v>665918</v>
       </c>
       <c r="R29" t="n">
-        <v>7185668</v>
+        <v>7185620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3548,44 +3384,39 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119880455</v>
+        <v>119880472</v>
       </c>
       <c r="B30" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6286</v>
+        <v>3100</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3595,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>665872</v>
+        <v>665998</v>
       </c>
       <c r="R30" t="n">
-        <v>7185555</v>
+        <v>7185666</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3657,15 +3488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119880456</v>
+        <v>119880410</v>
       </c>
       <c r="B31" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,21 +3499,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3697,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>665872</v>
+        <v>665646</v>
       </c>
       <c r="R31" t="n">
-        <v>7185563</v>
+        <v>7185686</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3759,15 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119880452</v>
+        <v>119880430</v>
       </c>
       <c r="B32" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3775,21 +3596,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3799,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>665842</v>
+        <v>665527</v>
       </c>
       <c r="R32" t="n">
-        <v>7185565</v>
+        <v>7185533</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3861,15 +3682,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119880446</v>
+        <v>119880454</v>
       </c>
       <c r="B33" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,21 +3693,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3901,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>665779</v>
+        <v>665867</v>
       </c>
       <c r="R33" t="n">
-        <v>7185598</v>
+        <v>7185544</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,22 +3772,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119880442</v>
+        <v>119880460</v>
       </c>
       <c r="B34" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3979,21 +3790,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4003,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>665744</v>
+        <v>665910</v>
       </c>
       <c r="R34" t="n">
-        <v>7185572</v>
+        <v>7185584</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4058,22 +3869,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119880449</v>
+        <v>119880466</v>
       </c>
       <c r="B35" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4081,21 +3887,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4105,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>665811</v>
+        <v>665966</v>
       </c>
       <c r="R35" t="n">
-        <v>7185566</v>
+        <v>7185634</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,15 +3973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119880414</v>
+        <v>119880479</v>
       </c>
       <c r="B36" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4183,21 +3984,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4207,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>665625</v>
+        <v>666021</v>
       </c>
       <c r="R36" t="n">
-        <v>7185661</v>
+        <v>7185711</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,15 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119880444</v>
+        <v>119880424</v>
       </c>
       <c r="B37" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4285,21 +4081,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4309,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>665746</v>
+        <v>665577</v>
       </c>
       <c r="R37" t="n">
-        <v>7185579</v>
+        <v>7185596</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4371,37 +4167,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119880461</v>
+        <v>119880433</v>
       </c>
       <c r="B38" t="n">
-        <v>91862</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>665905</v>
+        <v>665516</v>
       </c>
       <c r="R38" t="n">
-        <v>7185598</v>
+        <v>7185504</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4466,22 +4257,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119880450</v>
+        <v>119880441</v>
       </c>
       <c r="B39" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4489,21 +4275,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4513,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>665811</v>
+        <v>665740</v>
       </c>
       <c r="R39" t="n">
-        <v>7185566</v>
+        <v>7185522</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4568,22 +4354,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119880459</v>
+        <v>119880442</v>
       </c>
       <c r="B40" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4591,21 +4372,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4615,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>665913</v>
+        <v>665744</v>
       </c>
       <c r="R40" t="n">
-        <v>7185574</v>
+        <v>7185572</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4670,22 +4451,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119880419</v>
+        <v>119880448</v>
       </c>
       <c r="B41" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4693,21 +4469,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4717,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>665600</v>
+        <v>665801</v>
       </c>
       <c r="R41" t="n">
-        <v>7185629</v>
+        <v>7185555</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4772,44 +4548,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119880438</v>
+        <v>119880411</v>
       </c>
       <c r="B42" t="n">
-        <v>91862</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4819,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>665723</v>
+        <v>665645</v>
       </c>
       <c r="R42" t="n">
-        <v>7185514</v>
+        <v>7185685</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4881,37 +4652,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119880460</v>
+        <v>119880438</v>
       </c>
       <c r="B43" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4921,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>665910</v>
+        <v>665723</v>
       </c>
       <c r="R43" t="n">
-        <v>7185584</v>
+        <v>7185514</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4976,44 +4742,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119880430</v>
+        <v>119880461</v>
       </c>
       <c r="B44" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5023,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>665527</v>
+        <v>665905</v>
       </c>
       <c r="R44" t="n">
-        <v>7185533</v>
+        <v>7185598</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5078,44 +4839,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119880468</v>
+        <v>119880478</v>
       </c>
       <c r="B45" t="n">
-        <v>79160</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5125,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>665975</v>
+        <v>666018</v>
       </c>
       <c r="R45" t="n">
-        <v>7185666</v>
+        <v>7185712</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5187,15 +4943,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119880433</v>
+        <v>119880397</v>
       </c>
       <c r="B46" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5203,21 +4954,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5227,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>665516</v>
+        <v>665844</v>
       </c>
       <c r="R46" t="n">
-        <v>7185504</v>
+        <v>7185751</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,37 +5040,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119880413</v>
+        <v>119880418</v>
       </c>
       <c r="B47" t="n">
-        <v>89292</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6286</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5329,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>665629</v>
+        <v>665618</v>
       </c>
       <c r="R47" t="n">
-        <v>7185671</v>
+        <v>7185647</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5391,37 +5137,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119880458</v>
+        <v>119880443</v>
       </c>
       <c r="B48" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5431,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>665911</v>
+        <v>665746</v>
       </c>
       <c r="R48" t="n">
-        <v>7185565</v>
+        <v>7185579</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5486,44 +5227,39 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119880471</v>
+        <v>119880457</v>
       </c>
       <c r="B49" t="n">
-        <v>91846</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5533,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>665988</v>
+        <v>665871</v>
       </c>
       <c r="R49" t="n">
-        <v>7185667</v>
+        <v>7185570</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5588,22 +5324,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119880431</v>
+        <v>119880464</v>
       </c>
       <c r="B50" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5611,21 +5342,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5635,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>665509</v>
+        <v>665922</v>
       </c>
       <c r="R50" t="n">
-        <v>7185520</v>
+        <v>7185624</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5690,44 +5421,39 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119880409</v>
+        <v>119880473</v>
       </c>
       <c r="B51" t="n">
-        <v>89247</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1596</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5737,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>665652</v>
+        <v>666000</v>
       </c>
       <c r="R51" t="n">
-        <v>7185701</v>
+        <v>7185668</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5799,15 +5525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119880441</v>
+        <v>119880475</v>
       </c>
       <c r="B52" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5815,21 +5536,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5839,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>665740</v>
+        <v>666018</v>
       </c>
       <c r="R52" t="n">
-        <v>7185522</v>
+        <v>7185712</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5901,37 +5622,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119880443</v>
+        <v>119880429</v>
       </c>
       <c r="B53" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5941,10 +5657,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>665746</v>
+        <v>665527</v>
       </c>
       <c r="R53" t="n">
-        <v>7185579</v>
+        <v>7185533</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6003,37 +5719,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119880440</v>
+        <v>119880458</v>
       </c>
       <c r="B54" t="n">
-        <v>78187</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6043,10 +5754,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>665733</v>
+        <v>665911</v>
       </c>
       <c r="R54" t="n">
-        <v>7185520</v>
+        <v>7185565</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6098,44 +5809,39 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119880448</v>
+        <v>119880462</v>
       </c>
       <c r="B55" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6145,10 +5851,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>665801</v>
+        <v>665918</v>
       </c>
       <c r="R55" t="n">
-        <v>7185555</v>
+        <v>7185620</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6200,44 +5906,39 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil Larsson, Magnus Wadstein</t>
+          <t>Magnus Wadstein, Emil Larsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119880429</v>
+        <v>119880467</v>
       </c>
       <c r="B56" t="n">
-        <v>91901</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5448</v>
+        <v>6276</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6247,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>665527</v>
+        <v>665967</v>
       </c>
       <c r="R56" t="n">
-        <v>7185533</v>
+        <v>7185660</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6309,15 +6010,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119880462</v>
+        <v>119880470</v>
       </c>
       <c r="B57" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6349,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>665918</v>
+        <v>665982</v>
       </c>
       <c r="R57" t="n">
-        <v>7185620</v>
+        <v>7185672</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6408,6 +6104,1097 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>119880474</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>666009</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7185710</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>119880398</v>
+      </c>
+      <c r="B59" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>665837</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7185742</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>119880400</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>665803</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7185746</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>119880405</v>
+      </c>
+      <c r="B61" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>665673</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7185728</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>119880413</v>
+      </c>
+      <c r="B62" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>665629</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7185671</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>119880455</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>665872</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7185555</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>118675822</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Falträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>665893</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7185443</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>119880468</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>665975</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7185666</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>119880437</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>665631</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7185482</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein, Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>119880417</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>665632</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7185649</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>119880423</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Nyängesbäckberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>665584</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7185605</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30159-2024 artfynd.xlsx
+++ b/artfynd/A 30159-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880465</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880412</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880414</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880419</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880427</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880431</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880434</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880440</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880445</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880446</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880449</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880451</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880456</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880459</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880476</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880406</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880409</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880407</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880425</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880439</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880444</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880450</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880447</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880452</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880453</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880463</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880472</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880410</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880430</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880454</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880460</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880466</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880479</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880424</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880433</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880441</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880442</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880448</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880411</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880438</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880461</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880478</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880397</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880418</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880443</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880457</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880464</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880473</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880475</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5716,6 +5976,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880429</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5813,6 +6078,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880458</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5910,6 +6180,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880462</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6007,6 +6282,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880467</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6104,6 +6384,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880470</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6201,6 +6486,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880474</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6298,6 +6588,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880398</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6395,6 +6690,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880400</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6492,6 +6792,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880405</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6589,6 +6894,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880413</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6686,6 +6996,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880455</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6792,6 +7107,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675822</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6889,6 +7209,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880468</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7001,6 +7326,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880437</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7098,6 +7428,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880417</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7195,8 +7530,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119880423</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>